--- a/research/traditional_assets/database/data/greece/greece_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_oil_gas_integrated.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1175330612616946</v>
+        <v>0.1173095885269189</v>
       </c>
       <c r="C2">
-        <v>218.987880927775</v>
+        <v>217.4668583854644</v>
       </c>
       <c r="D2">
-        <v>207.987880927775</v>
+        <v>208.6378583854644</v>
       </c>
       <c r="E2">
-        <v>-159.9</v>
+        <v>-157.729</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.171</v>
       </c>
       <c r="G2">
         <v>11</v>
@@ -1451,28 +1451,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1092013</v>
       </c>
       <c r="N2">
-        <v>37.53333333333333</v>
+        <v>37.42413203333333</v>
       </c>
       <c r="O2">
-        <v>8.257333333333333</v>
+        <v>8.233309047333332</v>
       </c>
       <c r="P2">
-        <v>29.276</v>
+        <v>29.190822986</v>
       </c>
       <c r="Q2">
-        <v>35.07599999999999</v>
+        <v>34.990822986</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1175330612616946</v>
+        <v>0.1180982308352716</v>
       </c>
       <c r="T2">
-        <v>0.934922259086021</v>
+        <v>0.9422883132485169</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>343.7077519528918</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1173095885269189</v>
+        <v>0.1170861157921431</v>
       </c>
       <c r="C3">
-        <v>217.4668583854644</v>
+        <v>215.9499110333474</v>
       </c>
       <c r="D3">
-        <v>208.6378583854644</v>
+        <v>209.2919110333474</v>
       </c>
       <c r="E3">
-        <v>-157.729</v>
+        <v>-155.558</v>
       </c>
       <c r="F3">
-        <v>2.171</v>
+        <v>4.342000000000001</v>
       </c>
       <c r="G3">
         <v>11</v>
@@ -1533,28 +1533,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M3">
-        <v>0.1092013</v>
+        <v>0.2184026</v>
       </c>
       <c r="N3">
-        <v>37.42413203333333</v>
+        <v>37.31493073333333</v>
       </c>
       <c r="O3">
-        <v>8.233309047333332</v>
+        <v>8.209284761333334</v>
       </c>
       <c r="P3">
-        <v>29.190822986</v>
+        <v>29.105645972</v>
       </c>
       <c r="Q3">
-        <v>34.990822986</v>
+        <v>34.905645972</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1180982308352716</v>
+        <v>0.1186749344817787</v>
       </c>
       <c r="T3">
-        <v>0.9422883132485169</v>
+        <v>0.9498046950469822</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>343.7077519528918</v>
+        <v>171.8538759764459</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1170861157921431</v>
+        <v>0.1168626430573674</v>
       </c>
       <c r="C4">
-        <v>215.9499110333474</v>
+        <v>214.4370773175272</v>
       </c>
       <c r="D4">
-        <v>209.2919110333474</v>
+        <v>209.9500773175272</v>
       </c>
       <c r="E4">
-        <v>-155.558</v>
+        <v>-153.387</v>
       </c>
       <c r="F4">
-        <v>4.342000000000001</v>
+        <v>6.513000000000001</v>
       </c>
       <c r="G4">
         <v>11</v>
@@ -1615,28 +1615,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M4">
-        <v>0.2184026</v>
+        <v>0.3276039</v>
       </c>
       <c r="N4">
-        <v>37.31493073333333</v>
+        <v>37.20572943333333</v>
       </c>
       <c r="O4">
-        <v>8.209284761333334</v>
+        <v>8.185260475333333</v>
       </c>
       <c r="P4">
-        <v>29.105645972</v>
+        <v>29.020468958</v>
       </c>
       <c r="Q4">
-        <v>34.905645972</v>
+        <v>34.820468958</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1186749344817787</v>
+        <v>0.119263528925121</v>
       </c>
       <c r="T4">
-        <v>0.9498046950469822</v>
+        <v>0.9574760537897457</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>171.8538759764459</v>
+        <v>114.569250650964</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1168626430573674</v>
+        <v>0.1166391703225917</v>
       </c>
       <c r="C5">
-        <v>214.4370773175272</v>
+        <v>212.9283961692425</v>
       </c>
       <c r="D5">
-        <v>209.9500773175272</v>
+        <v>210.6123961692425</v>
       </c>
       <c r="E5">
-        <v>-153.387</v>
+        <v>-151.216</v>
       </c>
       <c r="F5">
-        <v>6.513000000000001</v>
+        <v>8.684000000000001</v>
       </c>
       <c r="G5">
         <v>11</v>
@@ -1697,28 +1697,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M5">
-        <v>0.3276039</v>
+        <v>0.4368052</v>
       </c>
       <c r="N5">
-        <v>37.20572943333333</v>
+        <v>37.09652813333333</v>
       </c>
       <c r="O5">
-        <v>8.185260475333333</v>
+        <v>8.161236189333332</v>
       </c>
       <c r="P5">
-        <v>29.020468958</v>
+        <v>28.935291944</v>
       </c>
       <c r="Q5">
-        <v>34.820468958</v>
+        <v>34.735291944</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.119263528925121</v>
+        <v>0.1198643857526997</v>
       </c>
       <c r="T5">
-        <v>0.9574760537897457</v>
+        <v>0.9653072325063167</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>114.569250650964</v>
+        <v>85.92693798822296</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1166391703225917</v>
+        <v>0.1164156975878159</v>
       </c>
       <c r="C6">
-        <v>212.9283961692425</v>
+        <v>211.4239070125445</v>
       </c>
       <c r="D6">
-        <v>210.6123961692425</v>
+        <v>211.2789070125445</v>
       </c>
       <c r="E6">
-        <v>-151.216</v>
+        <v>-149.045</v>
       </c>
       <c r="F6">
-        <v>8.684000000000001</v>
+        <v>10.855</v>
       </c>
       <c r="G6">
         <v>11</v>
@@ -1779,28 +1779,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M6">
-        <v>0.4368052</v>
+        <v>0.5460065000000001</v>
       </c>
       <c r="N6">
-        <v>37.09652813333333</v>
+        <v>36.98732683333333</v>
       </c>
       <c r="O6">
-        <v>8.161236189333332</v>
+        <v>8.137211903333334</v>
       </c>
       <c r="P6">
-        <v>28.935291944</v>
+        <v>28.85011493</v>
       </c>
       <c r="Q6">
-        <v>34.735291944</v>
+        <v>34.65011493</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1198643857526997</v>
+        <v>0.120477892197701</v>
       </c>
       <c r="T6">
-        <v>0.9653072325063167</v>
+        <v>0.9733032781432367</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>85.92693798822296</v>
+        <v>68.74155039057837</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1164156975878159</v>
+        <v>0.1161922248530402</v>
       </c>
       <c r="C7">
-        <v>211.4239070125445</v>
+        <v>209.923649772119</v>
       </c>
       <c r="D7">
-        <v>211.2789070125445</v>
+        <v>211.949649772119</v>
       </c>
       <c r="E7">
-        <v>-149.045</v>
+        <v>-146.874</v>
       </c>
       <c r="F7">
-        <v>10.855</v>
+        <v>13.026</v>
       </c>
       <c r="G7">
         <v>11</v>
@@ -1861,28 +1861,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M7">
-        <v>0.5460065000000001</v>
+        <v>0.6552078</v>
       </c>
       <c r="N7">
-        <v>36.98732683333333</v>
+        <v>36.87812553333333</v>
       </c>
       <c r="O7">
-        <v>8.137211903333334</v>
+        <v>8.113187617333333</v>
       </c>
       <c r="P7">
-        <v>28.85011493</v>
+        <v>28.764937916</v>
       </c>
       <c r="Q7">
-        <v>34.65011493</v>
+        <v>34.56493791600001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.120477892197701</v>
+        <v>0.1211044519713194</v>
       </c>
       <c r="T7">
-        <v>0.9733032781432367</v>
+        <v>0.9814694524107292</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>68.74155039057837</v>
+        <v>57.28462532548198</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1161922248530402</v>
+        <v>0.1159687521182645</v>
       </c>
       <c r="C8">
-        <v>209.923649772119</v>
+        <v>208.427664881259</v>
       </c>
       <c r="D8">
-        <v>211.949649772119</v>
+        <v>212.624664881259</v>
       </c>
       <c r="E8">
-        <v>-146.874</v>
+        <v>-144.703</v>
       </c>
       <c r="F8">
-        <v>13.026</v>
+        <v>15.197</v>
       </c>
       <c r="G8">
         <v>11</v>
@@ -1943,28 +1943,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M8">
-        <v>0.6552078</v>
+        <v>0.7644091</v>
       </c>
       <c r="N8">
-        <v>36.87812553333333</v>
+        <v>36.76892423333333</v>
       </c>
       <c r="O8">
-        <v>8.113187617333333</v>
+        <v>8.089163331333333</v>
       </c>
       <c r="P8">
-        <v>28.764937916</v>
+        <v>28.679760902</v>
       </c>
       <c r="Q8">
-        <v>34.56493791600001</v>
+        <v>34.479760902</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1211044519713194</v>
+        <v>0.1217444861486715</v>
       </c>
       <c r="T8">
-        <v>0.9814694524107292</v>
+        <v>0.9898112433291357</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>57.28462532548198</v>
+        <v>49.1011074218417</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1159687521182645</v>
+        <v>0.1157452793834888</v>
       </c>
       <c r="C9">
-        <v>208.427664881259</v>
+        <v>206.9359932899894</v>
       </c>
       <c r="D9">
-        <v>212.624664881259</v>
+        <v>213.3039932899894</v>
       </c>
       <c r="E9">
-        <v>-144.703</v>
+        <v>-142.532</v>
       </c>
       <c r="F9">
-        <v>15.197</v>
+        <v>17.368</v>
       </c>
       <c r="G9">
         <v>11</v>
@@ -2025,28 +2025,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M9">
-        <v>0.7644091000000001</v>
+        <v>0.8736104</v>
       </c>
       <c r="N9">
-        <v>36.76892423333333</v>
+        <v>36.65972293333333</v>
       </c>
       <c r="O9">
-        <v>8.089163331333333</v>
+        <v>8.065139045333334</v>
       </c>
       <c r="P9">
-        <v>28.679760902</v>
+        <v>28.594583888</v>
       </c>
       <c r="Q9">
-        <v>34.479760902</v>
+        <v>34.394583888</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1217444861486715</v>
+        <v>0.1223984341124878</v>
       </c>
       <c r="T9">
-        <v>0.9898112433291358</v>
+        <v>0.9983343775283772</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>49.10110742184169</v>
+        <v>42.96346899411149</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1157452793834888</v>
+        <v>0.1155218066487131</v>
       </c>
       <c r="C10">
-        <v>206.9359932899894</v>
+        <v>205.4486764733479</v>
       </c>
       <c r="D10">
-        <v>213.3039932899894</v>
+        <v>213.9876764733479</v>
       </c>
       <c r="E10">
-        <v>-142.532</v>
+        <v>-140.361</v>
       </c>
       <c r="F10">
-        <v>17.368</v>
+        <v>19.539</v>
       </c>
       <c r="G10">
         <v>11</v>
@@ -2107,28 +2107,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M10">
-        <v>0.8736104</v>
+        <v>0.9828117000000001</v>
       </c>
       <c r="N10">
-        <v>36.65972293333333</v>
+        <v>36.55052163333333</v>
       </c>
       <c r="O10">
-        <v>8.065139045333334</v>
+        <v>8.041114759333333</v>
       </c>
       <c r="P10">
-        <v>28.594583888</v>
+        <v>28.509406874</v>
       </c>
       <c r="Q10">
-        <v>34.394583888</v>
+        <v>34.309406874</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1223984341124878</v>
+        <v>0.1230667545590253</v>
       </c>
       <c r="T10">
-        <v>0.9983343775283772</v>
+        <v>1.007044833358371</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>42.96346899411149</v>
+        <v>38.18975021698798</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1155218066487131</v>
+        <v>0.1152983339139373</v>
       </c>
       <c r="C11">
-        <v>205.4486764733479</v>
+        <v>203.9657564398263</v>
       </c>
       <c r="D11">
-        <v>213.9876764733479</v>
+        <v>214.6757564398263</v>
       </c>
       <c r="E11">
-        <v>-140.361</v>
+        <v>-138.19</v>
       </c>
       <c r="F11">
-        <v>19.539</v>
+        <v>21.71</v>
       </c>
       <c r="G11">
         <v>11</v>
@@ -2189,28 +2189,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M11">
-        <v>0.9828117000000001</v>
+        <v>1.092013</v>
       </c>
       <c r="N11">
-        <v>36.55052163333333</v>
+        <v>36.44132033333333</v>
       </c>
       <c r="O11">
-        <v>8.041114759333333</v>
+        <v>8.017090473333333</v>
       </c>
       <c r="P11">
-        <v>28.509406874</v>
+        <v>28.42422986</v>
       </c>
       <c r="Q11">
-        <v>34.309406874</v>
+        <v>34.22422985999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1230667545590253</v>
+        <v>0.1237499265710414</v>
       </c>
       <c r="T11">
-        <v>1.007044833358371</v>
+        <v>1.015948854873476</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>38.18975021698798</v>
+        <v>34.37077519528919</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1152983339139373</v>
+        <v>0.1150748611791616</v>
       </c>
       <c r="C12">
-        <v>203.9657564398263</v>
+        <v>202.4872757399745</v>
       </c>
       <c r="D12">
-        <v>214.6757564398263</v>
+        <v>215.3682757399745</v>
       </c>
       <c r="E12">
-        <v>-138.19</v>
+        <v>-136.019</v>
       </c>
       <c r="F12">
-        <v>21.71</v>
+        <v>23.881</v>
       </c>
       <c r="G12">
         <v>11</v>
@@ -2271,28 +2271,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M12">
-        <v>1.092013</v>
+        <v>1.2012143</v>
       </c>
       <c r="N12">
-        <v>36.44132033333333</v>
+        <v>36.33211903333333</v>
       </c>
       <c r="O12">
-        <v>8.017090473333333</v>
+        <v>7.993066187333332</v>
       </c>
       <c r="P12">
-        <v>28.42422986</v>
+        <v>28.33905284599999</v>
       </c>
       <c r="Q12">
-        <v>34.22422985999999</v>
+        <v>34.139052846</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1237499265710414</v>
+        <v>0.1244484507631029</v>
       </c>
       <c r="T12">
-        <v>1.015948854873476</v>
+        <v>1.025052966759707</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>34.37077519528918</v>
+        <v>31.24615926844471</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1150748611791616</v>
+        <v>0.1148513884443859</v>
       </c>
       <c r="C13">
-        <v>202.4872757399745</v>
+        <v>201.0132774751721</v>
       </c>
       <c r="D13">
-        <v>215.3682757399745</v>
+        <v>216.0652774751721</v>
       </c>
       <c r="E13">
-        <v>-136.019</v>
+        <v>-133.848</v>
       </c>
       <c r="F13">
-        <v>23.881</v>
+        <v>26.052</v>
       </c>
       <c r="G13">
         <v>11</v>
@@ -2353,28 +2353,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M13">
-        <v>1.2012143</v>
+        <v>1.3104156</v>
       </c>
       <c r="N13">
-        <v>36.33211903333333</v>
+        <v>36.22291773333333</v>
       </c>
       <c r="O13">
-        <v>7.993066187333332</v>
+        <v>7.969041901333333</v>
       </c>
       <c r="P13">
-        <v>28.33905284599999</v>
+        <v>28.253875832</v>
       </c>
       <c r="Q13">
-        <v>34.139052846</v>
+        <v>34.053875832</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1244484507631029</v>
+        <v>0.1251628505049839</v>
       </c>
       <c r="T13">
-        <v>1.025052966759707</v>
+        <v>1.034363990279716</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>31.24615926844471</v>
+        <v>28.64231266274099</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1148513884443859</v>
+        <v>0.1146279157096101</v>
       </c>
       <c r="C14">
-        <v>201.0132774751721</v>
+        <v>199.5438053065708</v>
       </c>
       <c r="D14">
-        <v>216.0652774751721</v>
+        <v>216.7668053065709</v>
       </c>
       <c r="E14">
-        <v>-133.848</v>
+        <v>-131.677</v>
       </c>
       <c r="F14">
-        <v>26.052</v>
+        <v>28.223</v>
       </c>
       <c r="G14">
         <v>11</v>
@@ -2435,28 +2435,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M14">
-        <v>1.3104156</v>
+        <v>1.4196169</v>
       </c>
       <c r="N14">
-        <v>36.22291773333333</v>
+        <v>36.11371643333333</v>
       </c>
       <c r="O14">
-        <v>7.969041901333333</v>
+        <v>7.945017615333333</v>
       </c>
       <c r="P14">
-        <v>28.253875832</v>
+        <v>28.168698818</v>
       </c>
       <c r="Q14">
-        <v>34.053875832</v>
+        <v>33.96869881799999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1251628505049839</v>
+        <v>0.1258936732294369</v>
       </c>
       <c r="T14">
-        <v>1.034363990279716</v>
+        <v>1.043889060317426</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>28.64231266274099</v>
+        <v>26.43905784253014</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1146279157096101</v>
+        <v>0.1144044429748344</v>
       </c>
       <c r="C15">
-        <v>199.5438053065708</v>
+        <v>198.078903464211</v>
       </c>
       <c r="D15">
-        <v>216.7668053065709</v>
+        <v>217.472903464211</v>
       </c>
       <c r="E15">
-        <v>-131.677</v>
+        <v>-129.506</v>
       </c>
       <c r="F15">
-        <v>28.223</v>
+        <v>30.39400000000001</v>
       </c>
       <c r="G15">
         <v>11</v>
@@ -2517,28 +2517,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M15">
-        <v>1.4196169</v>
+        <v>1.5288182</v>
       </c>
       <c r="N15">
-        <v>36.11371643333333</v>
+        <v>36.00451513333333</v>
       </c>
       <c r="O15">
-        <v>7.945017615333333</v>
+        <v>7.920993329333332</v>
       </c>
       <c r="P15">
-        <v>28.168698818</v>
+        <v>28.083521804</v>
       </c>
       <c r="Q15">
-        <v>33.96869881799999</v>
+        <v>33.883521804</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1258936732294369</v>
+        <v>0.1266414918312028</v>
       </c>
       <c r="T15">
-        <v>1.043889060317426</v>
+        <v>1.053635643611827</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>26.43905784253014</v>
+        <v>24.55055371092084</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1144044429748344</v>
+        <v>0.1141809702400587</v>
       </c>
       <c r="C16">
-        <v>198.078903464211</v>
+        <v>196.6186167563177</v>
       </c>
       <c r="D16">
-        <v>217.472903464211</v>
+        <v>218.1836167563177</v>
       </c>
       <c r="E16">
-        <v>-129.506</v>
+        <v>-127.335</v>
       </c>
       <c r="F16">
-        <v>30.39400000000001</v>
+        <v>32.565</v>
       </c>
       <c r="G16">
         <v>11</v>
@@ -2599,28 +2599,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M16">
-        <v>1.5288182</v>
+        <v>1.6380195</v>
       </c>
       <c r="N16">
-        <v>36.00451513333333</v>
+        <v>35.89531383333333</v>
       </c>
       <c r="O16">
-        <v>7.920993329333332</v>
+        <v>7.896969043333333</v>
       </c>
       <c r="P16">
-        <v>28.083521804</v>
+        <v>27.99834479</v>
       </c>
       <c r="Q16">
-        <v>33.883521804</v>
+        <v>33.79834479</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1266414918312028</v>
+        <v>0.1274069061647749</v>
       </c>
       <c r="T16">
-        <v>1.053635643611827</v>
+        <v>1.063611558277862</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>24.55055371092084</v>
+        <v>22.91385013019279</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1141809702400587</v>
+        <v>0.1139574975052829</v>
       </c>
       <c r="C17">
-        <v>196.6186167563177</v>
+        <v>195.1629905787797</v>
       </c>
       <c r="D17">
-        <v>218.1836167563177</v>
+        <v>218.8989905787797</v>
       </c>
       <c r="E17">
-        <v>-127.335</v>
+        <v>-125.164</v>
       </c>
       <c r="F17">
-        <v>32.565</v>
+        <v>34.736</v>
       </c>
       <c r="G17">
         <v>11</v>
@@ -2681,28 +2681,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M17">
-        <v>1.6380195</v>
+        <v>1.7472208</v>
       </c>
       <c r="N17">
-        <v>35.89531383333333</v>
+        <v>35.78611253333333</v>
       </c>
       <c r="O17">
-        <v>7.896969043333333</v>
+        <v>7.872944757333332</v>
       </c>
       <c r="P17">
-        <v>27.99834479</v>
+        <v>27.913167776</v>
       </c>
       <c r="Q17">
-        <v>33.79834479</v>
+        <v>33.713167776</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1274069061647749</v>
+        <v>0.1281905446491464</v>
       </c>
       <c r="T17">
-        <v>1.063611558277862</v>
+        <v>1.073824994721658</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>22.91385013019279</v>
+        <v>21.48173449705574</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1139574975052829</v>
+        <v>0.1137340247705072</v>
       </c>
       <c r="C18">
-        <v>195.1629905787797</v>
+        <v>193.7120709248144</v>
       </c>
       <c r="D18">
-        <v>218.8989905787797</v>
+        <v>219.6190709248144</v>
       </c>
       <c r="E18">
-        <v>-125.164</v>
+        <v>-122.993</v>
       </c>
       <c r="F18">
-        <v>34.736</v>
+        <v>36.907</v>
       </c>
       <c r="G18">
         <v>11</v>
@@ -2763,28 +2763,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M18">
-        <v>1.7472208</v>
+        <v>1.8564221</v>
       </c>
       <c r="N18">
-        <v>35.78611253333333</v>
+        <v>35.67691123333333</v>
       </c>
       <c r="O18">
-        <v>7.872944757333332</v>
+        <v>7.848920471333332</v>
       </c>
       <c r="P18">
-        <v>27.913167776</v>
+        <v>27.827990762</v>
       </c>
       <c r="Q18">
-        <v>33.713167776</v>
+        <v>33.627990762</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1281905446491464</v>
+        <v>0.1289930659885629</v>
       </c>
       <c r="T18">
-        <v>1.073824994721658</v>
+        <v>1.084284538067716</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>21.48173449705574</v>
+        <v>20.21810305605246</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1137340247705072</v>
+        <v>0.1135105520357315</v>
       </c>
       <c r="C19">
-        <v>193.7120709248144</v>
+        <v>192.2659043948262</v>
       </c>
       <c r="D19">
-        <v>219.6190709248144</v>
+        <v>220.3439043948262</v>
       </c>
       <c r="E19">
-        <v>-122.993</v>
+        <v>-120.822</v>
       </c>
       <c r="F19">
-        <v>36.907</v>
+        <v>39.07800000000001</v>
       </c>
       <c r="G19">
         <v>11</v>
@@ -2845,28 +2845,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M19">
-        <v>1.8564221</v>
+        <v>1.9656234</v>
       </c>
       <c r="N19">
-        <v>35.67691123333333</v>
+        <v>35.56770993333333</v>
       </c>
       <c r="O19">
-        <v>7.848920471333332</v>
+        <v>7.824896185333333</v>
       </c>
       <c r="P19">
-        <v>27.827990762</v>
+        <v>27.742813748</v>
       </c>
       <c r="Q19">
-        <v>33.627990762</v>
+        <v>33.542813748</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1289930659885629</v>
+        <v>0.1298151610191847</v>
       </c>
       <c r="T19">
-        <v>1.084284538067716</v>
+        <v>1.094999192227091</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>20.21810305605246</v>
+        <v>19.09487510849399</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1135105520357315</v>
+        <v>0.1132870793009558</v>
       </c>
       <c r="C20">
-        <v>192.2659043948262</v>
+        <v>190.8245382064583</v>
       </c>
       <c r="D20">
-        <v>220.3439043948262</v>
+        <v>221.0735382064583</v>
       </c>
       <c r="E20">
-        <v>-120.822</v>
+        <v>-118.651</v>
       </c>
       <c r="F20">
-        <v>39.078</v>
+        <v>41.249</v>
       </c>
       <c r="G20">
         <v>11</v>
@@ -2927,28 +2927,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M20">
-        <v>1.9656234</v>
+        <v>2.0748247</v>
       </c>
       <c r="N20">
-        <v>35.56770993333333</v>
+        <v>35.45850863333333</v>
       </c>
       <c r="O20">
-        <v>7.824896185333333</v>
+        <v>7.800871899333333</v>
       </c>
       <c r="P20">
-        <v>27.742813748</v>
+        <v>27.657636734</v>
       </c>
       <c r="Q20">
-        <v>33.542813748</v>
+        <v>33.457636734</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1298151610191847</v>
+        <v>0.130657554692538</v>
       </c>
       <c r="T20">
-        <v>1.094999192227091</v>
+        <v>1.105978405748426</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>19.09487510849399</v>
+        <v>18.08988168173115</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1132870793009558</v>
+        <v>0.11306360656618</v>
       </c>
       <c r="C21">
-        <v>190.8245382064583</v>
+        <v>189.3880202048468</v>
       </c>
       <c r="D21">
-        <v>221.0735382064583</v>
+        <v>221.8080202048468</v>
       </c>
       <c r="E21">
-        <v>-118.651</v>
+        <v>-116.48</v>
       </c>
       <c r="F21">
-        <v>41.249</v>
+        <v>43.42000000000001</v>
       </c>
       <c r="G21">
         <v>11</v>
@@ -3009,28 +3009,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M21">
-        <v>2.0748247</v>
+        <v>2.184026</v>
       </c>
       <c r="N21">
-        <v>35.45850863333333</v>
+        <v>35.34930733333333</v>
       </c>
       <c r="O21">
-        <v>7.800871899333333</v>
+        <v>7.776847613333333</v>
       </c>
       <c r="P21">
-        <v>27.657636734</v>
+        <v>27.57245972</v>
       </c>
       <c r="Q21">
-        <v>33.457636734</v>
+        <v>33.37245971999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.130657554692538</v>
+        <v>0.131521008207725</v>
       </c>
       <c r="T21">
-        <v>1.105978405748426</v>
+        <v>1.117232099607795</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>18.08988168173115</v>
+        <v>17.18538759764459</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.11306360656618</v>
+        <v>0.1128401338314043</v>
       </c>
       <c r="C22">
-        <v>189.3880202048468</v>
+        <v>187.9563988730788</v>
       </c>
       <c r="D22">
-        <v>221.8080202048468</v>
+        <v>222.5473988730788</v>
       </c>
       <c r="E22">
-        <v>-116.48</v>
+        <v>-114.309</v>
       </c>
       <c r="F22">
-        <v>43.42000000000001</v>
+        <v>45.59100000000001</v>
       </c>
       <c r="G22">
         <v>11</v>
@@ -3091,28 +3091,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M22">
-        <v>2.184026</v>
+        <v>2.2932273</v>
       </c>
       <c r="N22">
-        <v>35.34930733333333</v>
+        <v>35.24010603333333</v>
       </c>
       <c r="O22">
-        <v>7.776847613333333</v>
+        <v>7.752823327333333</v>
       </c>
       <c r="P22">
-        <v>27.57245972</v>
+        <v>27.487282706</v>
       </c>
       <c r="Q22">
-        <v>33.37245971999999</v>
+        <v>33.287282706</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.131521008207725</v>
+        <v>0.1324063213055751</v>
       </c>
       <c r="T22">
-        <v>1.117232099607795</v>
+        <v>1.128770697109173</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>17.18538759764459</v>
+        <v>16.36703580728057</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1128401338314043</v>
+        <v>0.1126166610966286</v>
       </c>
       <c r="C23">
-        <v>187.9563988730789</v>
+        <v>186.5297233428615</v>
       </c>
       <c r="D23">
-        <v>222.5473988730789</v>
+        <v>223.2917233428615</v>
       </c>
       <c r="E23">
-        <v>-114.309</v>
+        <v>-112.138</v>
       </c>
       <c r="F23">
-        <v>45.591</v>
+        <v>47.76200000000001</v>
       </c>
       <c r="G23">
         <v>11</v>
@@ -3173,28 +3173,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M23">
-        <v>2.2932273</v>
+        <v>2.4024286</v>
       </c>
       <c r="N23">
-        <v>35.24010603333333</v>
+        <v>35.13090473333333</v>
       </c>
       <c r="O23">
-        <v>7.752823327333333</v>
+        <v>7.728799041333333</v>
       </c>
       <c r="P23">
-        <v>27.487282706</v>
+        <v>27.402105692</v>
       </c>
       <c r="Q23">
-        <v>33.287282706</v>
+        <v>33.202105692</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1324063213055751</v>
+        <v>0.1333143347392674</v>
       </c>
       <c r="T23">
-        <v>1.128770697109173</v>
+        <v>1.140605156084946</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>16.36703580728057</v>
+        <v>15.62307963422236</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1126166610966286</v>
+        <v>0.1123931883618528</v>
       </c>
       <c r="C24">
-        <v>186.5297233428615</v>
+        <v>185.1080434054041</v>
       </c>
       <c r="D24">
-        <v>223.2917233428615</v>
+        <v>224.0410434054041</v>
       </c>
       <c r="E24">
-        <v>-112.138</v>
+        <v>-109.967</v>
       </c>
       <c r="F24">
-        <v>47.76200000000001</v>
+        <v>49.93300000000001</v>
       </c>
       <c r="G24">
         <v>11</v>
@@ -3255,28 +3255,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M24">
-        <v>2.4024286</v>
+        <v>2.5116299</v>
       </c>
       <c r="N24">
-        <v>35.13090473333333</v>
+        <v>35.02170343333333</v>
       </c>
       <c r="O24">
-        <v>7.728799041333333</v>
+        <v>7.704774755333332</v>
       </c>
       <c r="P24">
-        <v>27.402105692</v>
+        <v>27.316928678</v>
       </c>
       <c r="Q24">
-        <v>33.202105692</v>
+        <v>33.11692867799999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1333143347392674</v>
+        <v>0.1342459329374712</v>
       </c>
       <c r="T24">
-        <v>1.140605156084946</v>
+        <v>1.152747003605543</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>15.62307963422236</v>
+        <v>14.94381530229964</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1123931883618528</v>
+        <v>0.1121697156270771</v>
       </c>
       <c r="C25">
-        <v>185.1080434054041</v>
+        <v>183.6914095225219</v>
       </c>
       <c r="D25">
-        <v>224.0410434054041</v>
+        <v>224.7954095225219</v>
       </c>
       <c r="E25">
-        <v>-109.967</v>
+        <v>-107.796</v>
       </c>
       <c r="F25">
-        <v>49.93300000000001</v>
+        <v>52.10400000000001</v>
       </c>
       <c r="G25">
         <v>11</v>
@@ -3337,28 +3337,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M25">
-        <v>2.5116299</v>
+        <v>2.6208312</v>
       </c>
       <c r="N25">
-        <v>35.02170343333333</v>
+        <v>34.91250213333333</v>
       </c>
       <c r="O25">
-        <v>7.704774755333332</v>
+        <v>7.680750469333334</v>
       </c>
       <c r="P25">
-        <v>27.316928678</v>
+        <v>27.231751664</v>
       </c>
       <c r="Q25">
-        <v>33.11692867799999</v>
+        <v>33.031751664</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1342459329374712</v>
+        <v>0.135202046877733</v>
       </c>
       <c r="T25">
-        <v>1.152747003605543</v>
+        <v>1.165208373429315</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.94381530229964</v>
+        <v>14.3211563313705</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1121697156270771</v>
+        <v>0.1119462428923014</v>
       </c>
       <c r="C26">
-        <v>183.6914095225219</v>
+        <v>182.2798728379641</v>
       </c>
       <c r="D26">
-        <v>224.7954095225219</v>
+        <v>225.5548728379641</v>
       </c>
       <c r="E26">
-        <v>-107.796</v>
+        <v>-105.625</v>
       </c>
       <c r="F26">
-        <v>52.10400000000001</v>
+        <v>54.27500000000001</v>
       </c>
       <c r="G26">
         <v>11</v>
@@ -3419,28 +3419,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M26">
-        <v>2.6208312</v>
+        <v>2.7300325</v>
       </c>
       <c r="N26">
-        <v>34.91250213333333</v>
+        <v>34.80330083333333</v>
       </c>
       <c r="O26">
-        <v>7.680750469333334</v>
+        <v>7.656726183333333</v>
       </c>
       <c r="P26">
-        <v>27.231751664</v>
+        <v>27.14657465</v>
       </c>
       <c r="Q26">
-        <v>33.031751664</v>
+        <v>32.94657465</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.135202046877733</v>
+        <v>0.1361836571897352</v>
       </c>
       <c r="T26">
-        <v>1.165208373429315</v>
+        <v>1.178002046448386</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>14.3211563313705</v>
+        <v>13.74831007811567</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1119462428923014</v>
+        <v>0.1117227701575257</v>
       </c>
       <c r="C27">
-        <v>182.2798728379641</v>
+        <v>180.8734851889718</v>
       </c>
       <c r="D27">
-        <v>225.5548728379641</v>
+        <v>226.3194851889718</v>
       </c>
       <c r="E27">
-        <v>-105.625</v>
+        <v>-103.454</v>
       </c>
       <c r="F27">
-        <v>54.27500000000001</v>
+        <v>56.44600000000001</v>
       </c>
       <c r="G27">
         <v>11</v>
@@ -3501,28 +3501,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M27">
-        <v>2.7300325</v>
+        <v>2.8392338</v>
       </c>
       <c r="N27">
-        <v>34.80330083333333</v>
+        <v>34.69409953333333</v>
       </c>
       <c r="O27">
-        <v>7.656726183333333</v>
+        <v>7.632701897333332</v>
       </c>
       <c r="P27">
-        <v>27.14657465</v>
+        <v>27.061397636</v>
       </c>
       <c r="Q27">
-        <v>32.94657465</v>
+        <v>32.86139763599999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1361836571897352</v>
+        <v>0.1371917975101698</v>
       </c>
       <c r="T27">
-        <v>1.178002046448386</v>
+        <v>1.19114149441392</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>13.74831007811567</v>
+        <v>13.21952892126507</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1117227701575257</v>
+        <v>0.1118151974227499</v>
       </c>
       <c r="C28">
-        <v>180.8734851889718</v>
+        <v>178.3856173782308</v>
       </c>
       <c r="D28">
-        <v>226.3194851889718</v>
+        <v>226.0026173782308</v>
       </c>
       <c r="E28">
-        <v>-103.454</v>
+        <v>-101.283</v>
       </c>
       <c r="F28">
-        <v>56.44600000000001</v>
+        <v>58.61700000000001</v>
       </c>
       <c r="G28">
         <v>11</v>
@@ -3583,45 +3583,45 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M28">
-        <v>2.8392338</v>
+        <v>3.036360600000001</v>
       </c>
       <c r="N28">
-        <v>34.69409953333333</v>
+        <v>34.49697273333333</v>
       </c>
       <c r="O28">
-        <v>7.632701897333332</v>
+        <v>7.589334001333333</v>
       </c>
       <c r="P28">
-        <v>27.061397636</v>
+        <v>26.907638732</v>
       </c>
       <c r="Q28">
-        <v>32.86139763599999</v>
+        <v>32.70763873199999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1371917975101698</v>
+        <v>0.1382275581133561</v>
       </c>
       <c r="T28">
-        <v>1.19114149441392</v>
+        <v>1.204640927255221</v>
       </c>
       <c r="U28">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V28">
         <v>0.22</v>
       </c>
       <c r="W28">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y28">
-        <v>13.21952892126507</v>
+        <v>12.36128980639958</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1118151974227499</v>
+        <v>0.1116034246879742</v>
       </c>
       <c r="C29">
-        <v>178.3856173782308</v>
+        <v>176.9419532665316</v>
       </c>
       <c r="D29">
-        <v>226.0026173782308</v>
+        <v>226.7299532665316</v>
       </c>
       <c r="E29">
-        <v>-101.283</v>
+        <v>-99.11199999999999</v>
       </c>
       <c r="F29">
-        <v>58.61700000000001</v>
+        <v>60.78800000000001</v>
       </c>
       <c r="G29">
         <v>11</v>
@@ -3665,28 +3665,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M29">
-        <v>3.036360600000001</v>
+        <v>3.148818400000001</v>
       </c>
       <c r="N29">
-        <v>34.49697273333333</v>
+        <v>34.38451493333333</v>
       </c>
       <c r="O29">
-        <v>7.589334001333333</v>
+        <v>7.564593285333332</v>
       </c>
       <c r="P29">
-        <v>26.907638732</v>
+        <v>26.819921648</v>
       </c>
       <c r="Q29">
-        <v>32.70763873199999</v>
+        <v>32.619921648</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1382275581133561</v>
+        <v>0.1392920898444086</v>
       </c>
       <c r="T29">
-        <v>1.204640927255221</v>
+        <v>1.218515344342114</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>12.36128980639958</v>
+        <v>11.91981517045674</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1116034246879742</v>
+        <v>0.1113916519531985</v>
       </c>
       <c r="C30">
-        <v>176.9419532665316</v>
+        <v>175.5029857863573</v>
       </c>
       <c r="D30">
-        <v>226.7299532665316</v>
+        <v>227.4619857863573</v>
       </c>
       <c r="E30">
-        <v>-99.11199999999999</v>
+        <v>-96.94099999999999</v>
       </c>
       <c r="F30">
-        <v>60.78800000000001</v>
+        <v>62.95900000000002</v>
       </c>
       <c r="G30">
         <v>11</v>
@@ -3747,28 +3747,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M30">
-        <v>3.148818400000001</v>
+        <v>3.261276200000001</v>
       </c>
       <c r="N30">
-        <v>34.38451493333333</v>
+        <v>34.27205713333333</v>
       </c>
       <c r="O30">
-        <v>7.564593285333332</v>
+        <v>7.539852569333333</v>
       </c>
       <c r="P30">
-        <v>26.819921648</v>
+        <v>26.732204564</v>
       </c>
       <c r="Q30">
-        <v>32.619921648</v>
+        <v>32.532204564</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1392920898444086</v>
+        <v>0.1403866083847866</v>
       </c>
       <c r="T30">
-        <v>1.218515344342114</v>
+        <v>1.232780590079342</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.91981517045674</v>
+        <v>11.50878706113065</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1113916519531985</v>
+        <v>0.1111798792184227</v>
       </c>
       <c r="C31">
-        <v>175.5029857863573</v>
+        <v>174.0687605764509</v>
       </c>
       <c r="D31">
-        <v>227.4619857863573</v>
+        <v>228.1987605764509</v>
       </c>
       <c r="E31">
-        <v>-96.941</v>
+        <v>-94.77</v>
       </c>
       <c r="F31">
-        <v>62.959</v>
+        <v>65.13000000000001</v>
       </c>
       <c r="G31">
         <v>11</v>
@@ -3829,28 +3829,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M31">
-        <v>3.2612762</v>
+        <v>3.373734</v>
       </c>
       <c r="N31">
-        <v>34.27205713333333</v>
+        <v>34.15959933333333</v>
       </c>
       <c r="O31">
-        <v>7.539852569333333</v>
+        <v>7.515111853333333</v>
       </c>
       <c r="P31">
-        <v>26.732204564</v>
+        <v>26.64448748</v>
       </c>
       <c r="Q31">
-        <v>32.532204564</v>
+        <v>32.44448748</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1403866083847866</v>
+        <v>0.1415123988834611</v>
       </c>
       <c r="T31">
-        <v>1.232780590079342</v>
+        <v>1.247453414266205</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.50878706113065</v>
+        <v>11.12516082575963</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1111798792184227</v>
+        <v>0.110968106483647</v>
       </c>
       <c r="C32">
-        <v>174.0687605764509</v>
+        <v>172.6393238687928</v>
       </c>
       <c r="D32">
-        <v>228.1987605764509</v>
+        <v>228.9403238687928</v>
       </c>
       <c r="E32">
-        <v>-94.77</v>
+        <v>-92.599</v>
       </c>
       <c r="F32">
-        <v>65.13000000000001</v>
+        <v>67.301</v>
       </c>
       <c r="G32">
         <v>11</v>
@@ -3911,28 +3911,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M32">
-        <v>3.373734</v>
+        <v>3.4861918</v>
       </c>
       <c r="N32">
-        <v>34.15959933333333</v>
+        <v>34.04714153333333</v>
       </c>
       <c r="O32">
-        <v>7.515111853333333</v>
+        <v>7.490371137333333</v>
       </c>
       <c r="P32">
-        <v>26.64448748</v>
+        <v>26.556770396</v>
       </c>
       <c r="Q32">
-        <v>32.44448748</v>
+        <v>32.356770396</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1415123988834611</v>
+        <v>0.1426708209907928</v>
       </c>
       <c r="T32">
-        <v>1.247453414266205</v>
+        <v>1.262551537704862</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.12516082575963</v>
+        <v>10.76628467008996</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.110968106483647</v>
+        <v>0.1107563337488713</v>
       </c>
       <c r="C33">
-        <v>172.6393238687928</v>
+        <v>171.2147224982717</v>
       </c>
       <c r="D33">
-        <v>228.9403238687928</v>
+        <v>229.6867224982717</v>
       </c>
       <c r="E33">
-        <v>-92.599</v>
+        <v>-90.428</v>
       </c>
       <c r="F33">
-        <v>67.301</v>
+        <v>69.47200000000001</v>
       </c>
       <c r="G33">
         <v>11</v>
@@ -3993,28 +3993,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M33">
-        <v>3.4861918</v>
+        <v>3.5986496</v>
       </c>
       <c r="N33">
-        <v>34.04714153333333</v>
+        <v>33.93468373333333</v>
       </c>
       <c r="O33">
-        <v>7.490371137333333</v>
+        <v>7.465630421333333</v>
       </c>
       <c r="P33">
-        <v>26.556770396</v>
+        <v>26.469053312</v>
       </c>
       <c r="Q33">
-        <v>32.356770396</v>
+        <v>32.269053312</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1426708209907928</v>
+        <v>0.1438633143365755</v>
       </c>
       <c r="T33">
-        <v>1.262551537704862</v>
+        <v>1.278093723597596</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.76628467008996</v>
+        <v>10.42983827414965</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1107563337488713</v>
+        <v>0.1105445610140956</v>
       </c>
       <c r="C34">
-        <v>171.2147224982717</v>
+        <v>169.7950039125444</v>
       </c>
       <c r="D34">
-        <v>229.6867224982717</v>
+        <v>230.4380039125444</v>
       </c>
       <c r="E34">
-        <v>-90.428</v>
+        <v>-88.25699999999999</v>
       </c>
       <c r="F34">
-        <v>69.47200000000001</v>
+        <v>71.64300000000001</v>
       </c>
       <c r="G34">
         <v>11</v>
@@ -4075,28 +4075,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M34">
-        <v>3.5986496</v>
+        <v>3.711107400000001</v>
       </c>
       <c r="N34">
-        <v>33.93468373333333</v>
+        <v>33.82222593333333</v>
       </c>
       <c r="O34">
-        <v>7.465630421333333</v>
+        <v>7.440889705333332</v>
       </c>
       <c r="P34">
-        <v>26.469053312</v>
+        <v>26.381336228</v>
       </c>
       <c r="Q34">
-        <v>32.269053312</v>
+        <v>32.18133622799999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1438633143365755</v>
+        <v>0.1450914044986501</v>
       </c>
       <c r="T34">
-        <v>1.278093723597596</v>
+        <v>1.294099855337874</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.42983827414965</v>
+        <v>10.11378256887239</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1105445610140956</v>
+        <v>0.1103327882793198</v>
       </c>
       <c r="C35">
-        <v>169.7950039125444</v>
+        <v>168.3802161820902</v>
       </c>
       <c r="D35">
-        <v>230.4380039125444</v>
+        <v>231.1942161820902</v>
       </c>
       <c r="E35">
-        <v>-88.25699999999999</v>
+        <v>-86.086</v>
       </c>
       <c r="F35">
-        <v>71.64300000000001</v>
+        <v>73.81400000000001</v>
       </c>
       <c r="G35">
         <v>11</v>
@@ -4157,28 +4157,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M35">
-        <v>3.711107400000001</v>
+        <v>3.8235652</v>
       </c>
       <c r="N35">
-        <v>33.82222593333333</v>
+        <v>33.70976813333333</v>
       </c>
       <c r="O35">
-        <v>7.440889705333332</v>
+        <v>7.416148989333333</v>
       </c>
       <c r="P35">
-        <v>26.381336228</v>
+        <v>26.293619144</v>
       </c>
       <c r="Q35">
-        <v>32.18133622799999</v>
+        <v>32.093619144</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1450914044986501</v>
+        <v>0.146356709514121</v>
       </c>
       <c r="T35">
-        <v>1.294099855337874</v>
+        <v>1.310591021373313</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>10.11378256887239</v>
+        <v>9.81631837567026</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1103327882793198</v>
+        <v>0.1105851155445441</v>
       </c>
       <c r="C36">
-        <v>168.3802161820902</v>
+        <v>165.3087531079017</v>
       </c>
       <c r="D36">
-        <v>231.1942161820902</v>
+        <v>230.2937531079017</v>
       </c>
       <c r="E36">
-        <v>-86.086</v>
+        <v>-83.91499999999999</v>
       </c>
       <c r="F36">
-        <v>73.81400000000001</v>
+        <v>75.98500000000001</v>
       </c>
       <c r="G36">
         <v>11</v>
@@ -4239,45 +4239,45 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M36">
-        <v>3.8235652</v>
+        <v>4.065197500000001</v>
       </c>
       <c r="N36">
-        <v>33.70976813333333</v>
+        <v>33.46813583333333</v>
       </c>
       <c r="O36">
-        <v>7.416148989333333</v>
+        <v>7.362989883333332</v>
       </c>
       <c r="P36">
-        <v>26.293619144</v>
+        <v>26.10514594999999</v>
       </c>
       <c r="Q36">
-        <v>32.093619144</v>
+        <v>31.90514594999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.146356709514121</v>
+        <v>0.1476609469916063</v>
       </c>
       <c r="T36">
-        <v>1.310591021373313</v>
+        <v>1.32758960790215</v>
       </c>
       <c r="U36">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V36">
         <v>0.22</v>
       </c>
       <c r="W36">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>9.81631837567026</v>
+        <v>9.232843750723875</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1105851155445441</v>
+        <v>0.1103866028097684</v>
       </c>
       <c r="C37">
-        <v>165.3087531079017</v>
+        <v>163.8455816782612</v>
       </c>
       <c r="D37">
-        <v>230.2937531079017</v>
+        <v>231.0015816782612</v>
       </c>
       <c r="E37">
-        <v>-83.91499999999999</v>
+        <v>-81.74399999999999</v>
       </c>
       <c r="F37">
-        <v>75.98500000000001</v>
+        <v>78.15600000000002</v>
       </c>
       <c r="G37">
         <v>11</v>
@@ -4321,28 +4321,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M37">
-        <v>4.065197500000001</v>
+        <v>4.181346000000001</v>
       </c>
       <c r="N37">
-        <v>33.46813583333333</v>
+        <v>33.35198733333333</v>
       </c>
       <c r="O37">
-        <v>7.362989883333332</v>
+        <v>7.337437213333332</v>
       </c>
       <c r="P37">
-        <v>26.10514594999999</v>
+        <v>26.01455012</v>
       </c>
       <c r="Q37">
-        <v>31.90514594999999</v>
+        <v>31.81455012</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1476609469916063</v>
+        <v>0.1490059418902631</v>
       </c>
       <c r="T37">
-        <v>1.32758960790215</v>
+        <v>1.345119400260013</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>9.232843750723875</v>
+        <v>8.976375868759323</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1103866028097684</v>
+        <v>0.1101880900749927</v>
       </c>
       <c r="C38">
-        <v>163.8455816782612</v>
+        <v>162.386774813095</v>
       </c>
       <c r="D38">
-        <v>231.0015816782612</v>
+        <v>231.713774813095</v>
       </c>
       <c r="E38">
-        <v>-81.744</v>
+        <v>-79.57299999999999</v>
       </c>
       <c r="F38">
-        <v>78.15600000000001</v>
+        <v>80.32700000000001</v>
       </c>
       <c r="G38">
         <v>11</v>
@@ -4403,28 +4403,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M38">
-        <v>4.181346</v>
+        <v>4.297494500000001</v>
       </c>
       <c r="N38">
-        <v>33.35198733333333</v>
+        <v>33.23583883333333</v>
       </c>
       <c r="O38">
-        <v>7.337437213333334</v>
+        <v>7.311884543333333</v>
       </c>
       <c r="P38">
-        <v>26.01455012</v>
+        <v>25.92395429</v>
       </c>
       <c r="Q38">
-        <v>31.81455012</v>
+        <v>31.72395429</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1490059418902631</v>
+        <v>0.1503936350396709</v>
       </c>
       <c r="T38">
-        <v>1.345119400260013</v>
+        <v>1.36320569396257</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.976375868759325</v>
+        <v>8.733771115549612</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1101880900749927</v>
+        <v>0.1099895773402169</v>
       </c>
       <c r="C39">
-        <v>162.386774813095</v>
+        <v>160.9323730059692</v>
       </c>
       <c r="D39">
-        <v>231.713774813095</v>
+        <v>232.4303730059692</v>
       </c>
       <c r="E39">
-        <v>-79.57299999999999</v>
+        <v>-77.402</v>
       </c>
       <c r="F39">
-        <v>80.32700000000001</v>
+        <v>82.498</v>
       </c>
       <c r="G39">
         <v>11</v>
@@ -4485,28 +4485,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M39">
-        <v>4.297494500000001</v>
+        <v>4.413643</v>
       </c>
       <c r="N39">
-        <v>33.23583883333333</v>
+        <v>33.11969033333333</v>
       </c>
       <c r="O39">
-        <v>7.311884543333333</v>
+        <v>7.286331873333332</v>
       </c>
       <c r="P39">
-        <v>25.92395429</v>
+        <v>25.83335846</v>
       </c>
       <c r="Q39">
-        <v>31.72395429</v>
+        <v>31.63335846</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1503936350396709</v>
+        <v>0.1518260924842208</v>
       </c>
       <c r="T39">
-        <v>1.36320569396257</v>
+        <v>1.381875416494241</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.733771115549612</v>
+        <v>8.503935033561465</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1099895773402169</v>
+        <v>0.1097910646054412</v>
       </c>
       <c r="C40">
-        <v>160.9323730059692</v>
+        <v>159.4824172529254</v>
       </c>
       <c r="D40">
-        <v>232.4303730059692</v>
+        <v>233.1514172529254</v>
       </c>
       <c r="E40">
-        <v>-77.402</v>
+        <v>-75.23099999999999</v>
       </c>
       <c r="F40">
-        <v>82.498</v>
+        <v>84.66900000000001</v>
       </c>
       <c r="G40">
         <v>11</v>
@@ -4567,28 +4567,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M40">
-        <v>4.413643</v>
+        <v>4.529791500000001</v>
       </c>
       <c r="N40">
-        <v>33.11969033333333</v>
+        <v>33.00354183333333</v>
       </c>
       <c r="O40">
-        <v>7.286331873333332</v>
+        <v>7.260779203333333</v>
       </c>
       <c r="P40">
-        <v>25.83335846</v>
+        <v>25.74276263</v>
       </c>
       <c r="Q40">
-        <v>31.63335846</v>
+        <v>31.54276263</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1518260924842208</v>
+        <v>0.1533055157466249</v>
       </c>
       <c r="T40">
-        <v>1.381875416494241</v>
+        <v>1.401157261076132</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.503935033561465</v>
+        <v>8.285885417316299</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1097910646054412</v>
+        <v>0.1095925518706655</v>
       </c>
       <c r="C41">
-        <v>159.4824172529254</v>
+        <v>158.0369490602993</v>
       </c>
       <c r="D41">
-        <v>233.1514172529254</v>
+        <v>233.8769490602993</v>
       </c>
       <c r="E41">
-        <v>-75.23099999999999</v>
+        <v>-73.05999999999999</v>
       </c>
       <c r="F41">
-        <v>84.66900000000001</v>
+        <v>86.84000000000002</v>
       </c>
       <c r="G41">
         <v>11</v>
@@ -4649,28 +4649,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M41">
-        <v>4.529791500000001</v>
+        <v>4.645940000000001</v>
       </c>
       <c r="N41">
-        <v>33.00354183333333</v>
+        <v>32.88739333333333</v>
       </c>
       <c r="O41">
-        <v>7.260779203333333</v>
+        <v>7.235226533333332</v>
       </c>
       <c r="P41">
-        <v>25.74276263</v>
+        <v>25.6521668</v>
       </c>
       <c r="Q41">
-        <v>31.54276263</v>
+        <v>31.4521668</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1533055157466249</v>
+        <v>0.1548342531177758</v>
       </c>
       <c r="T41">
-        <v>1.401157261076132</v>
+        <v>1.421081833810752</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.285885417316299</v>
+        <v>8.078738281883391</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1095925518706655</v>
+        <v>0.1093940391358897</v>
       </c>
       <c r="C42">
-        <v>158.0369490602993</v>
+        <v>156.5960104526847</v>
       </c>
       <c r="D42">
-        <v>233.8769490602993</v>
+        <v>234.6070104526847</v>
       </c>
       <c r="E42">
-        <v>-73.05999999999999</v>
+        <v>-70.889</v>
       </c>
       <c r="F42">
-        <v>86.84000000000002</v>
+        <v>89.01100000000001</v>
       </c>
       <c r="G42">
         <v>11</v>
@@ -4731,28 +4731,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M42">
-        <v>4.645940000000001</v>
+        <v>4.762088500000001</v>
       </c>
       <c r="N42">
-        <v>32.88739333333333</v>
+        <v>32.77124483333333</v>
       </c>
       <c r="O42">
-        <v>7.235226533333332</v>
+        <v>7.209673863333332</v>
       </c>
       <c r="P42">
-        <v>25.6521668</v>
+        <v>25.56157096999999</v>
       </c>
       <c r="Q42">
-        <v>31.4521668</v>
+        <v>31.36157097</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1548342531177758</v>
+        <v>0.1564148120947284</v>
       </c>
       <c r="T42">
-        <v>1.421081833810752</v>
+        <v>1.441681815790613</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.078738281883391</v>
+        <v>7.881695884764284</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1093940391358897</v>
+        <v>0.109195526401114</v>
       </c>
       <c r="C43">
-        <v>156.5960104526847</v>
+        <v>155.1596439810484</v>
       </c>
       <c r="D43">
-        <v>234.6070104526847</v>
+        <v>235.3416439810484</v>
       </c>
       <c r="E43">
-        <v>-70.889</v>
+        <v>-68.71799999999999</v>
       </c>
       <c r="F43">
-        <v>89.01100000000001</v>
+        <v>91.18200000000002</v>
       </c>
       <c r="G43">
         <v>11</v>
@@ -4813,28 +4813,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M43">
-        <v>4.762088500000001</v>
+        <v>4.878237</v>
       </c>
       <c r="N43">
-        <v>32.77124483333333</v>
+        <v>32.65509633333333</v>
       </c>
       <c r="O43">
-        <v>7.209673863333332</v>
+        <v>7.184121193333334</v>
       </c>
       <c r="P43">
-        <v>25.56157096999999</v>
+        <v>25.47097514</v>
       </c>
       <c r="Q43">
-        <v>31.36157097</v>
+        <v>31.27097514</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1564148120947284</v>
+        <v>0.158049873105369</v>
       </c>
       <c r="T43">
-        <v>1.441681815790613</v>
+        <v>1.462992141976677</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.881695884764284</v>
+        <v>7.694036458936565</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.109195526401114</v>
+        <v>0.1092653336663383</v>
       </c>
       <c r="C44">
-        <v>155.1596439810483</v>
+        <v>152.7297852370595</v>
       </c>
       <c r="D44">
-        <v>235.3416439810483</v>
+        <v>235.0827852370595</v>
       </c>
       <c r="E44">
-        <v>-68.718</v>
+        <v>-66.547</v>
       </c>
       <c r="F44">
-        <v>91.182</v>
+        <v>93.35300000000001</v>
       </c>
       <c r="G44">
         <v>11</v>
@@ -4895,45 +4895,45 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M44">
-        <v>4.878237</v>
+        <v>5.0690679</v>
       </c>
       <c r="N44">
-        <v>32.65509633333333</v>
+        <v>32.46426543333333</v>
       </c>
       <c r="O44">
-        <v>7.184121193333334</v>
+        <v>7.142138395333333</v>
       </c>
       <c r="P44">
-        <v>25.47097514</v>
+        <v>25.322127038</v>
       </c>
       <c r="Q44">
-        <v>31.27097514</v>
+        <v>31.122127038</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.158049873105369</v>
+        <v>0.1597423046777865</v>
       </c>
       <c r="T44">
-        <v>1.462992141976677</v>
+        <v>1.485050198906111</v>
       </c>
       <c r="U44">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V44">
         <v>0.22</v>
       </c>
       <c r="W44">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y44">
-        <v>7.694036458936565</v>
+        <v>7.404385593914284</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1092653336663383</v>
+        <v>0.1090730609315626</v>
       </c>
       <c r="C45">
-        <v>152.7297852370595</v>
+        <v>151.2731494443658</v>
       </c>
       <c r="D45">
-        <v>235.0827852370595</v>
+        <v>235.7971494443658</v>
       </c>
       <c r="E45">
-        <v>-66.547</v>
+        <v>-64.37599999999999</v>
       </c>
       <c r="F45">
-        <v>93.35300000000001</v>
+        <v>95.52400000000002</v>
       </c>
       <c r="G45">
         <v>11</v>
@@ -4977,28 +4977,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M45">
-        <v>5.0690679</v>
+        <v>5.1869532</v>
       </c>
       <c r="N45">
-        <v>32.46426543333333</v>
+        <v>32.34638013333333</v>
       </c>
       <c r="O45">
-        <v>7.142138395333333</v>
+        <v>7.116203629333334</v>
       </c>
       <c r="P45">
-        <v>25.322127038</v>
+        <v>25.230176504</v>
       </c>
       <c r="Q45">
-        <v>31.122127038</v>
+        <v>31.030176504</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1597423046777865</v>
+        <v>0.1614951802349331</v>
       </c>
       <c r="T45">
-        <v>1.485050198906111</v>
+        <v>1.507896043583025</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.404385593914284</v>
+        <v>7.236104103143504</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1090730609315626</v>
+        <v>0.1088807881967868</v>
       </c>
       <c r="C46">
-        <v>151.2731494443658</v>
+        <v>149.8208684723297</v>
       </c>
       <c r="D46">
-        <v>235.7971494443658</v>
+        <v>236.5158684723297</v>
       </c>
       <c r="E46">
-        <v>-64.37599999999999</v>
+        <v>-62.205</v>
       </c>
       <c r="F46">
-        <v>95.52400000000002</v>
+        <v>97.69500000000001</v>
       </c>
       <c r="G46">
         <v>11</v>
@@ -5059,28 +5059,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M46">
-        <v>5.1869532</v>
+        <v>5.304838500000001</v>
       </c>
       <c r="N46">
-        <v>32.34638013333333</v>
+        <v>32.22849483333333</v>
       </c>
       <c r="O46">
-        <v>7.116203629333334</v>
+        <v>7.090268863333333</v>
       </c>
       <c r="P46">
-        <v>25.230176504</v>
+        <v>25.13822597</v>
       </c>
       <c r="Q46">
-        <v>31.030176504</v>
+        <v>30.93822597</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1614951802349331</v>
+        <v>0.1633117967214306</v>
       </c>
       <c r="T46">
-        <v>1.507896043583025</v>
+        <v>1.531572646248191</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>7.236104103143504</v>
+        <v>7.075301789740315</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1088807881967868</v>
+        <v>0.1086885154620111</v>
       </c>
       <c r="C47">
-        <v>149.8208684723297</v>
+        <v>148.3729822636945</v>
       </c>
       <c r="D47">
-        <v>236.5158684723297</v>
+        <v>237.2389822636945</v>
       </c>
       <c r="E47">
-        <v>-62.205</v>
+        <v>-60.03399999999999</v>
       </c>
       <c r="F47">
-        <v>97.69500000000001</v>
+        <v>99.86600000000001</v>
       </c>
       <c r="G47">
         <v>11</v>
@@ -5141,28 +5141,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M47">
-        <v>5.304838500000001</v>
+        <v>5.422723800000001</v>
       </c>
       <c r="N47">
-        <v>32.22849483333333</v>
+        <v>32.11060953333333</v>
       </c>
       <c r="O47">
-        <v>7.090268863333333</v>
+        <v>7.064334097333333</v>
       </c>
       <c r="P47">
-        <v>25.13822597</v>
+        <v>25.046275436</v>
       </c>
       <c r="Q47">
-        <v>30.93822597</v>
+        <v>30.846275436</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1633117967214306</v>
+        <v>0.1651956953000205</v>
       </c>
       <c r="T47">
-        <v>1.531572646248191</v>
+        <v>1.556126160123177</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.075301789740315</v>
+        <v>6.921490881267699</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1086885154620111</v>
+        <v>0.1084962427272354</v>
       </c>
       <c r="C48">
-        <v>148.3729822636945</v>
+        <v>146.9295312511784</v>
       </c>
       <c r="D48">
-        <v>237.2389822636945</v>
+        <v>237.9665312511784</v>
       </c>
       <c r="E48">
-        <v>-60.03399999999999</v>
+        <v>-57.86299999999999</v>
       </c>
       <c r="F48">
-        <v>99.86600000000001</v>
+        <v>102.037</v>
       </c>
       <c r="G48">
         <v>11</v>
@@ -5223,28 +5223,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M48">
-        <v>5.422723800000001</v>
+        <v>5.540609100000001</v>
       </c>
       <c r="N48">
-        <v>32.11060953333333</v>
+        <v>31.99272423333333</v>
       </c>
       <c r="O48">
-        <v>7.064334097333333</v>
+        <v>7.038399331333332</v>
       </c>
       <c r="P48">
-        <v>25.046275436</v>
+        <v>24.954324902</v>
       </c>
       <c r="Q48">
-        <v>30.846275436</v>
+        <v>30.754324902</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1651956953000205</v>
+        <v>0.1671506843910101</v>
       </c>
       <c r="T48">
-        <v>1.556126160123177</v>
+        <v>1.581606221691559</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.921490881267699</v>
+        <v>6.774225117836471</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1084962427272354</v>
+        <v>0.1083039699924597</v>
       </c>
       <c r="C49">
-        <v>146.9295312511784</v>
+        <v>145.4905563650115</v>
       </c>
       <c r="D49">
-        <v>237.9665312511784</v>
+        <v>238.6985563650115</v>
       </c>
       <c r="E49">
-        <v>-57.86299999999999</v>
+        <v>-55.69199999999999</v>
       </c>
       <c r="F49">
-        <v>102.037</v>
+        <v>104.208</v>
       </c>
       <c r="G49">
         <v>11</v>
@@ -5305,28 +5305,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M49">
-        <v>5.540609100000001</v>
+        <v>5.6584944</v>
       </c>
       <c r="N49">
-        <v>31.99272423333333</v>
+        <v>31.87483893333333</v>
       </c>
       <c r="O49">
-        <v>7.038399331333332</v>
+        <v>7.012464565333333</v>
       </c>
       <c r="P49">
-        <v>24.954324902</v>
+        <v>24.862374368</v>
       </c>
       <c r="Q49">
-        <v>30.754324902</v>
+        <v>30.662374368</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1671506843910101</v>
+        <v>0.1691808653701147</v>
       </c>
       <c r="T49">
-        <v>1.581606221691559</v>
+        <v>1.608066285627956</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.774225117836471</v>
+        <v>6.633095427881545</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1083039699924597</v>
+        <v>0.1081116972576839</v>
       </c>
       <c r="C50">
-        <v>145.4905563650116</v>
+        <v>144.0560990406111</v>
       </c>
       <c r="D50">
-        <v>238.6985563650116</v>
+        <v>239.4350990406111</v>
       </c>
       <c r="E50">
-        <v>-55.69199999999999</v>
+        <v>-53.521</v>
       </c>
       <c r="F50">
-        <v>104.208</v>
+        <v>106.379</v>
       </c>
       <c r="G50">
         <v>11</v>
@@ -5387,28 +5387,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M50">
-        <v>5.6584944</v>
+        <v>5.776379700000001</v>
       </c>
       <c r="N50">
-        <v>31.87483893333333</v>
+        <v>31.75695363333333</v>
       </c>
       <c r="O50">
-        <v>7.012464565333333</v>
+        <v>6.986529799333333</v>
       </c>
       <c r="P50">
-        <v>24.862374368</v>
+        <v>24.770423834</v>
       </c>
       <c r="Q50">
-        <v>30.662374368</v>
+        <v>30.570423834</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1691808653701147</v>
+        <v>0.1712906612895763</v>
       </c>
       <c r="T50">
-        <v>1.608066285627956</v>
+        <v>1.635563999130486</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.633095427881545</v>
+        <v>6.497726133434983</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1081116972576839</v>
+        <v>0.1079194245229082</v>
       </c>
       <c r="C51">
-        <v>144.0560990406111</v>
+        <v>142.6262012263994</v>
       </c>
       <c r="D51">
-        <v>239.4350990406111</v>
+        <v>240.1762012263994</v>
       </c>
       <c r="E51">
-        <v>-53.521</v>
+        <v>-51.34999999999999</v>
       </c>
       <c r="F51">
-        <v>106.379</v>
+        <v>108.55</v>
       </c>
       <c r="G51">
         <v>11</v>
@@ -5469,28 +5469,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M51">
-        <v>5.776379700000001</v>
+        <v>5.894265000000001</v>
       </c>
       <c r="N51">
-        <v>31.75695363333333</v>
+        <v>31.63906833333333</v>
       </c>
       <c r="O51">
-        <v>6.986529799333333</v>
+        <v>6.960595033333333</v>
       </c>
       <c r="P51">
-        <v>24.770423834</v>
+        <v>24.6784733</v>
       </c>
       <c r="Q51">
-        <v>30.570423834</v>
+        <v>30.4784733</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1712906612895763</v>
+        <v>0.1734848490458164</v>
       </c>
       <c r="T51">
-        <v>1.635563999130486</v>
+        <v>1.664161621173117</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.497726133434983</v>
+        <v>6.367771610766283</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1079194245229082</v>
+        <v>0.1077271517881325</v>
       </c>
       <c r="C52">
-        <v>142.6262012263994</v>
+        <v>141.2009053917683</v>
       </c>
       <c r="D52">
-        <v>240.1762012263994</v>
+        <v>240.9219053917683</v>
       </c>
       <c r="E52">
-        <v>-51.34999999999999</v>
+        <v>-49.17899999999999</v>
       </c>
       <c r="F52">
-        <v>108.55</v>
+        <v>110.721</v>
       </c>
       <c r="G52">
         <v>11</v>
@@ -5551,28 +5551,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M52">
-        <v>5.894265000000001</v>
+        <v>6.012150300000001</v>
       </c>
       <c r="N52">
-        <v>31.63906833333333</v>
+        <v>31.52118303333333</v>
       </c>
       <c r="O52">
-        <v>6.960595033333333</v>
+        <v>6.934660267333332</v>
       </c>
       <c r="P52">
-        <v>24.6784733</v>
+        <v>24.586522766</v>
       </c>
       <c r="Q52">
-        <v>30.4784733</v>
+        <v>30.386522766</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1734848490458164</v>
+        <v>0.1757685954859846</v>
       </c>
       <c r="T52">
-        <v>1.664161621173117</v>
+        <v>1.69392649309504</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.367771610766283</v>
+        <v>6.242913343888513</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1077271517881325</v>
+        <v>0.1075348790533567</v>
       </c>
       <c r="C53">
-        <v>141.2009053917683</v>
+        <v>139.7802545351921</v>
       </c>
       <c r="D53">
-        <v>240.9219053917683</v>
+        <v>241.6722545351921</v>
       </c>
       <c r="E53">
-        <v>-49.17899999999999</v>
+        <v>-47.008</v>
       </c>
       <c r="F53">
-        <v>110.721</v>
+        <v>112.892</v>
       </c>
       <c r="G53">
         <v>11</v>
@@ -5633,28 +5633,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M53">
-        <v>6.012150300000001</v>
+        <v>6.1300356</v>
       </c>
       <c r="N53">
-        <v>31.52118303333333</v>
+        <v>31.40329773333333</v>
       </c>
       <c r="O53">
-        <v>6.934660267333332</v>
+        <v>6.908725501333334</v>
       </c>
       <c r="P53">
-        <v>24.586522766</v>
+        <v>24.494572232</v>
       </c>
       <c r="Q53">
-        <v>30.386522766</v>
+        <v>30.294572232</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1757685954859846</v>
+        <v>0.1781474980278265</v>
       </c>
       <c r="T53">
-        <v>1.69392649309504</v>
+        <v>1.724931568013709</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.242913343888513</v>
+        <v>6.122857318044503</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1075348790533567</v>
+        <v>0.107756006318581</v>
       </c>
       <c r="C54">
-        <v>139.7802545351921</v>
+        <v>136.7467017674884</v>
       </c>
       <c r="D54">
-        <v>241.6722545351921</v>
+        <v>240.8097017674885</v>
       </c>
       <c r="E54">
-        <v>-47.008</v>
+        <v>-44.83699999999999</v>
       </c>
       <c r="F54">
-        <v>112.892</v>
+        <v>115.063</v>
       </c>
       <c r="G54">
         <v>11</v>
@@ -5715,45 +5715,45 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M54">
-        <v>6.1300356</v>
+        <v>6.362983900000001</v>
       </c>
       <c r="N54">
-        <v>31.40329773333333</v>
+        <v>31.17034943333333</v>
       </c>
       <c r="O54">
-        <v>6.908725501333334</v>
+        <v>6.857476875333332</v>
       </c>
       <c r="P54">
-        <v>24.494572232</v>
+        <v>24.312872558</v>
       </c>
       <c r="Q54">
-        <v>30.294572232</v>
+        <v>30.112872558</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1781474980278265</v>
+        <v>0.180627630465066</v>
       </c>
       <c r="T54">
-        <v>1.724931568013709</v>
+        <v>1.757256007822534</v>
       </c>
       <c r="U54">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V54">
         <v>0.22</v>
       </c>
       <c r="W54">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y54">
-        <v>6.122857318044503</v>
+        <v>5.898700031809498</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.107756006318581</v>
+        <v>0.1075715335838053</v>
       </c>
       <c r="C55">
-        <v>136.7467017674884</v>
+        <v>135.2948489485328</v>
       </c>
       <c r="D55">
-        <v>240.8097017674885</v>
+        <v>241.5288489485328</v>
       </c>
       <c r="E55">
-        <v>-44.83699999999999</v>
+        <v>-42.66599999999998</v>
       </c>
       <c r="F55">
-        <v>115.063</v>
+        <v>117.234</v>
       </c>
       <c r="G55">
         <v>11</v>
@@ -5797,28 +5797,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M55">
-        <v>6.362983900000001</v>
+        <v>6.483040200000001</v>
       </c>
       <c r="N55">
-        <v>31.17034943333333</v>
+        <v>31.05029313333333</v>
       </c>
       <c r="O55">
-        <v>6.857476875333332</v>
+        <v>6.831064489333333</v>
       </c>
       <c r="P55">
-        <v>24.312872558</v>
+        <v>24.219228644</v>
       </c>
       <c r="Q55">
-        <v>30.112872558</v>
+        <v>30.019228644</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.180627630465066</v>
+        <v>0.1832155947474028</v>
       </c>
       <c r="T55">
-        <v>1.757256007822534</v>
+        <v>1.79098585805783</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.898700031809498</v>
+        <v>5.789464846035248</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1075715335838053</v>
+        <v>0.1073870608490296</v>
       </c>
       <c r="C56">
-        <v>135.2948489485328</v>
+        <v>133.8473042763002</v>
       </c>
       <c r="D56">
-        <v>241.5288489485328</v>
+        <v>242.2523042763002</v>
       </c>
       <c r="E56">
-        <v>-42.66599999999998</v>
+        <v>-40.49499999999999</v>
       </c>
       <c r="F56">
-        <v>117.234</v>
+        <v>119.405</v>
       </c>
       <c r="G56">
         <v>11</v>
@@ -5879,28 +5879,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M56">
-        <v>6.483040200000001</v>
+        <v>6.603096500000001</v>
       </c>
       <c r="N56">
-        <v>31.05029313333333</v>
+        <v>30.93023683333333</v>
       </c>
       <c r="O56">
-        <v>6.831064489333333</v>
+        <v>6.804652103333333</v>
       </c>
       <c r="P56">
-        <v>24.219228644</v>
+        <v>24.12558473</v>
       </c>
       <c r="Q56">
-        <v>30.019228644</v>
+        <v>29.92558473</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1832155947474028</v>
+        <v>0.1859185796645101</v>
       </c>
       <c r="T56">
-        <v>1.79098585805783</v>
+        <v>1.826214812748028</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.789464846035248</v>
+        <v>5.684201848834608</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1073870608490296</v>
+        <v>0.1072025881142538</v>
       </c>
       <c r="C57">
-        <v>133.8473042763002</v>
+        <v>132.4041065798842</v>
       </c>
       <c r="D57">
-        <v>242.2523042763002</v>
+        <v>242.9801065798842</v>
       </c>
       <c r="E57">
-        <v>-40.49499999999999</v>
+        <v>-38.32399999999998</v>
       </c>
       <c r="F57">
-        <v>119.405</v>
+        <v>121.576</v>
       </c>
       <c r="G57">
         <v>11</v>
@@ -5961,28 +5961,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M57">
-        <v>6.603096500000001</v>
+        <v>6.723152800000001</v>
       </c>
       <c r="N57">
-        <v>30.93023683333333</v>
+        <v>30.81018053333333</v>
       </c>
       <c r="O57">
-        <v>6.804652103333333</v>
+        <v>6.778239717333332</v>
       </c>
       <c r="P57">
-        <v>24.12558473</v>
+        <v>24.031940816</v>
       </c>
       <c r="Q57">
-        <v>29.92558473</v>
+        <v>29.831940816</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1859185796645101</v>
+        <v>0.1887444275323951</v>
       </c>
       <c r="T57">
-        <v>1.826214812748028</v>
+        <v>1.863045083560507</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.684201848834608</v>
+        <v>5.582698244391132</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1072025881142538</v>
+        <v>0.1070181153794781</v>
       </c>
       <c r="C58">
-        <v>132.4041065798842</v>
+        <v>130.9652951564034</v>
       </c>
       <c r="D58">
-        <v>242.9801065798842</v>
+        <v>243.7122951564035</v>
       </c>
       <c r="E58">
-        <v>-38.32399999999998</v>
+        <v>-36.15299999999998</v>
       </c>
       <c r="F58">
-        <v>121.576</v>
+        <v>123.747</v>
       </c>
       <c r="G58">
         <v>11</v>
@@ -6043,28 +6043,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M58">
-        <v>6.723152800000001</v>
+        <v>6.843209100000002</v>
       </c>
       <c r="N58">
-        <v>30.81018053333333</v>
+        <v>30.69012423333333</v>
       </c>
       <c r="O58">
-        <v>6.778239717333332</v>
+        <v>6.751827331333332</v>
       </c>
       <c r="P58">
-        <v>24.031940816</v>
+        <v>23.938296902</v>
       </c>
       <c r="Q58">
-        <v>29.831940816</v>
+        <v>29.738296902</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1887444275323951</v>
+        <v>0.1917017101848328</v>
       </c>
       <c r="T58">
-        <v>1.863045083560507</v>
+        <v>1.90158839022473</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.582698244391132</v>
+        <v>5.484756169928129</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1070181153794781</v>
+        <v>0.1068336426447024</v>
       </c>
       <c r="C59">
-        <v>130.9652951564034</v>
+        <v>129.5309097780751</v>
       </c>
       <c r="D59">
-        <v>243.7122951564035</v>
+        <v>244.4489097780751</v>
       </c>
       <c r="E59">
-        <v>-36.15299999999998</v>
+        <v>-33.98199999999997</v>
       </c>
       <c r="F59">
-        <v>123.747</v>
+        <v>125.918</v>
       </c>
       <c r="G59">
         <v>11</v>
@@ -6125,28 +6125,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M59">
-        <v>6.843209100000002</v>
+        <v>6.963265400000002</v>
       </c>
       <c r="N59">
-        <v>30.69012423333333</v>
+        <v>30.57006793333333</v>
       </c>
       <c r="O59">
-        <v>6.751827331333332</v>
+        <v>6.725414945333333</v>
       </c>
       <c r="P59">
-        <v>23.938296902</v>
+        <v>23.844652988</v>
       </c>
       <c r="Q59">
-        <v>29.738296902</v>
+        <v>29.644652988</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1917017101848328</v>
+        <v>0.1947998158207199</v>
       </c>
       <c r="T59">
-        <v>1.90158839022473</v>
+        <v>1.941967092444392</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.484756169928129</v>
+        <v>5.390191408377644</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1068336426447024</v>
+        <v>0.1066491699099266</v>
       </c>
       <c r="C60">
-        <v>129.5309097780751</v>
+        <v>128.1009906994165</v>
       </c>
       <c r="D60">
-        <v>244.4489097780751</v>
+        <v>245.1899906994165</v>
       </c>
       <c r="E60">
-        <v>-33.982</v>
+        <v>-31.81100000000001</v>
       </c>
       <c r="F60">
-        <v>125.918</v>
+        <v>128.089</v>
       </c>
       <c r="G60">
         <v>11</v>
@@ -6207,28 +6207,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M60">
-        <v>6.963265400000001</v>
+        <v>7.0833217</v>
       </c>
       <c r="N60">
-        <v>30.57006793333333</v>
+        <v>30.45001163333333</v>
       </c>
       <c r="O60">
-        <v>6.725414945333333</v>
+        <v>6.699002559333334</v>
       </c>
       <c r="P60">
-        <v>23.844652988</v>
+        <v>23.751009074</v>
       </c>
       <c r="Q60">
-        <v>29.644652988</v>
+        <v>29.551009074</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1947998158207199</v>
+        <v>0.1980490485607966</v>
       </c>
       <c r="T60">
-        <v>1.941967092444392</v>
+        <v>1.984315487455257</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.390191408377645</v>
+        <v>5.298832231964465</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1066491699099266</v>
+        <v>0.1064646971751509</v>
       </c>
       <c r="C61">
-        <v>128.1009906994165</v>
+        <v>126.675578664578</v>
       </c>
       <c r="D61">
-        <v>245.1899906994165</v>
+        <v>245.9355786645779</v>
       </c>
       <c r="E61">
-        <v>-31.81100000000001</v>
+        <v>-29.63999999999999</v>
       </c>
       <c r="F61">
-        <v>128.089</v>
+        <v>130.26</v>
       </c>
       <c r="G61">
         <v>11</v>
@@ -6289,28 +6289,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M61">
-        <v>7.0833217</v>
+        <v>7.203378000000002</v>
       </c>
       <c r="N61">
-        <v>30.45001163333333</v>
+        <v>30.32995533333333</v>
       </c>
       <c r="O61">
-        <v>6.699002559333334</v>
+        <v>6.672590173333333</v>
       </c>
       <c r="P61">
-        <v>23.751009074</v>
+        <v>23.65736516</v>
       </c>
       <c r="Q61">
-        <v>29.551009074</v>
+        <v>29.45736516</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1980490485607966</v>
+        <v>0.2014607429378772</v>
       </c>
       <c r="T61">
-        <v>1.984315487455257</v>
+        <v>2.028781302216665</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.298832231964465</v>
+        <v>5.210518361431723</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1064646971751509</v>
+        <v>0.1062802244403752</v>
       </c>
       <c r="C62">
-        <v>126.675578664578</v>
+        <v>125.2547149148102</v>
       </c>
       <c r="D62">
-        <v>245.9355786645779</v>
+        <v>246.6857149148102</v>
       </c>
       <c r="E62">
-        <v>-29.63999999999999</v>
+        <v>-27.46899999999999</v>
       </c>
       <c r="F62">
-        <v>130.26</v>
+        <v>132.431</v>
       </c>
       <c r="G62">
         <v>11</v>
@@ -6371,28 +6371,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M62">
-        <v>7.203378000000002</v>
+        <v>7.323434300000001</v>
       </c>
       <c r="N62">
-        <v>30.32995533333333</v>
+        <v>30.20989903333333</v>
       </c>
       <c r="O62">
-        <v>6.672590173333333</v>
+        <v>6.646177787333333</v>
       </c>
       <c r="P62">
-        <v>23.65736516</v>
+        <v>23.563721246</v>
       </c>
       <c r="Q62">
-        <v>29.45736516</v>
+        <v>29.363721246</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2014607429378772</v>
+        <v>0.205047396000962</v>
       </c>
       <c r="T62">
-        <v>2.028781302216665</v>
+        <v>2.075527415170966</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.210518361431723</v>
+        <v>5.125100027637761</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1062802244403752</v>
+        <v>0.1060957517055995</v>
       </c>
       <c r="C63">
-        <v>125.2547149148102</v>
+        <v>123.8384411960684</v>
       </c>
       <c r="D63">
-        <v>246.6857149148102</v>
+        <v>247.4404411960684</v>
       </c>
       <c r="E63">
-        <v>-27.46899999999999</v>
+        <v>-25.298</v>
       </c>
       <c r="F63">
-        <v>132.431</v>
+        <v>134.602</v>
       </c>
       <c r="G63">
         <v>11</v>
@@ -6453,28 +6453,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M63">
-        <v>7.323434300000001</v>
+        <v>7.443490600000001</v>
       </c>
       <c r="N63">
-        <v>30.20989903333333</v>
+        <v>30.08984273333333</v>
       </c>
       <c r="O63">
-        <v>6.646177787333333</v>
+        <v>6.619765401333333</v>
       </c>
       <c r="P63">
-        <v>23.563721246</v>
+        <v>23.470077332</v>
       </c>
       <c r="Q63">
-        <v>29.363721246</v>
+        <v>29.270077332</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.205047396000962</v>
+        <v>0.2088228202778933</v>
       </c>
       <c r="T63">
-        <v>2.075527415170966</v>
+        <v>2.124733849859704</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.125100027637761</v>
+        <v>5.042437123966184</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1060957517055995</v>
+        <v>0.1059112789708237</v>
       </c>
       <c r="C64">
-        <v>123.8384411960684</v>
+        <v>122.4267997667571</v>
       </c>
       <c r="D64">
-        <v>247.4404411960684</v>
+        <v>248.1997997667571</v>
       </c>
       <c r="E64">
-        <v>-25.298</v>
+        <v>-23.12699999999998</v>
       </c>
       <c r="F64">
-        <v>134.602</v>
+        <v>136.773</v>
       </c>
       <c r="G64">
         <v>11</v>
@@ -6535,28 +6535,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M64">
-        <v>7.443490600000001</v>
+        <v>7.563546900000001</v>
       </c>
       <c r="N64">
-        <v>30.08984273333333</v>
+        <v>29.96978643333333</v>
       </c>
       <c r="O64">
-        <v>6.619765401333333</v>
+        <v>6.593353015333332</v>
       </c>
       <c r="P64">
-        <v>23.470077332</v>
+        <v>23.376433418</v>
       </c>
       <c r="Q64">
-        <v>29.270077332</v>
+        <v>29.176433418</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2088228202778933</v>
+        <v>0.2128023215427668</v>
       </c>
       <c r="T64">
-        <v>2.124733849859704</v>
+        <v>2.176600091828915</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.042437123966184</v>
+        <v>4.962398439458784</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1059112789708237</v>
+        <v>0.105726806236048</v>
       </c>
       <c r="C65">
-        <v>122.4267997667571</v>
+        <v>121.0198334056166</v>
       </c>
       <c r="D65">
-        <v>248.1997997667571</v>
+        <v>248.9638334056166</v>
       </c>
       <c r="E65">
-        <v>-23.12699999999998</v>
+        <v>-20.95599999999999</v>
       </c>
       <c r="F65">
-        <v>136.773</v>
+        <v>138.944</v>
       </c>
       <c r="G65">
         <v>11</v>
@@ -6617,28 +6617,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M65">
-        <v>7.563546900000001</v>
+        <v>7.683603200000001</v>
       </c>
       <c r="N65">
-        <v>29.96978643333333</v>
+        <v>29.84973013333333</v>
       </c>
       <c r="O65">
-        <v>6.593353015333332</v>
+        <v>6.566940629333333</v>
       </c>
       <c r="P65">
-        <v>23.376433418</v>
+        <v>23.282789504</v>
       </c>
       <c r="Q65">
-        <v>29.176433418</v>
+        <v>29.082789504</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2128023215427668</v>
+        <v>0.2170029062112444</v>
       </c>
       <c r="T65">
-        <v>2.176600091828915</v>
+        <v>2.231347791685304</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.962398439458784</v>
+        <v>4.884860963842241</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.105726806236048</v>
+        <v>0.1055423335012723</v>
       </c>
       <c r="C66">
-        <v>121.0198334056166</v>
+        <v>119.6175854197576</v>
       </c>
       <c r="D66">
-        <v>248.9638334056166</v>
+        <v>249.7325854197576</v>
       </c>
       <c r="E66">
-        <v>-20.95599999999999</v>
+        <v>-18.785</v>
       </c>
       <c r="F66">
-        <v>138.944</v>
+        <v>141.115</v>
       </c>
       <c r="G66">
         <v>11</v>
@@ -6699,28 +6699,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M66">
-        <v>7.683603200000001</v>
+        <v>7.803659500000001</v>
       </c>
       <c r="N66">
-        <v>29.84973013333333</v>
+        <v>29.72967383333333</v>
       </c>
       <c r="O66">
-        <v>6.566940629333333</v>
+        <v>6.540528243333332</v>
       </c>
       <c r="P66">
-        <v>23.282789504</v>
+        <v>23.18914559</v>
       </c>
       <c r="Q66">
-        <v>29.082789504</v>
+        <v>28.98914559</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2170029062112444</v>
+        <v>0.2214435242893494</v>
       </c>
       <c r="T66">
-        <v>2.231347791685304</v>
+        <v>2.289223931533486</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.884860963842241</v>
+        <v>4.809709256706206</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1055423335012723</v>
+        <v>0.1053578607664966</v>
       </c>
       <c r="C67">
-        <v>119.6175854197576</v>
+        <v>118.2200996528428</v>
       </c>
       <c r="D67">
-        <v>249.7325854197576</v>
+        <v>250.5060996528428</v>
       </c>
       <c r="E67">
-        <v>-18.785</v>
+        <v>-16.61399999999998</v>
       </c>
       <c r="F67">
-        <v>141.115</v>
+        <v>143.286</v>
       </c>
       <c r="G67">
         <v>11</v>
@@ -6781,28 +6781,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M67">
-        <v>7.803659500000001</v>
+        <v>7.923715800000002</v>
       </c>
       <c r="N67">
-        <v>29.72967383333333</v>
+        <v>29.60961753333333</v>
       </c>
       <c r="O67">
-        <v>6.540528243333332</v>
+        <v>6.514115857333332</v>
       </c>
       <c r="P67">
-        <v>23.18914559</v>
+        <v>23.095501676</v>
       </c>
       <c r="Q67">
-        <v>28.98914559</v>
+        <v>28.895501676</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2214435242893494</v>
+        <v>0.2261453551955781</v>
       </c>
       <c r="T67">
-        <v>2.289223931533486</v>
+        <v>2.350504550196268</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.809709256706206</v>
+        <v>4.736834874028839</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1053578607664966</v>
+        <v>0.1051733880317208</v>
       </c>
       <c r="C68">
-        <v>118.2200996528428</v>
+        <v>116.8274204934233</v>
       </c>
       <c r="D68">
-        <v>250.5060996528428</v>
+        <v>251.2844204934233</v>
       </c>
       <c r="E68">
-        <v>-16.61399999999998</v>
+        <v>-14.44299999999998</v>
       </c>
       <c r="F68">
-        <v>143.286</v>
+        <v>145.457</v>
       </c>
       <c r="G68">
         <v>11</v>
@@ -6863,28 +6863,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M68">
-        <v>7.923715800000002</v>
+        <v>8.043772100000002</v>
       </c>
       <c r="N68">
-        <v>29.60961753333333</v>
+        <v>29.48956123333333</v>
       </c>
       <c r="O68">
-        <v>6.514115857333332</v>
+        <v>6.487703471333332</v>
       </c>
       <c r="P68">
-        <v>23.095501676</v>
+        <v>23.001857762</v>
       </c>
       <c r="Q68">
-        <v>28.895501676</v>
+        <v>28.801857762</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2261453551955781</v>
+        <v>0.2311321455506692</v>
       </c>
       <c r="T68">
-        <v>2.350504550196268</v>
+        <v>2.415499145747702</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.736834874028839</v>
+        <v>4.66613584605826</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1051733880317208</v>
+        <v>0.1049889152969451</v>
       </c>
       <c r="C69">
-        <v>116.8274204934233</v>
+        <v>115.4395928834291</v>
       </c>
       <c r="D69">
-        <v>251.2844204934233</v>
+        <v>252.0675928834292</v>
       </c>
       <c r="E69">
-        <v>-14.44299999999998</v>
+        <v>-12.27199999999999</v>
       </c>
       <c r="F69">
-        <v>145.457</v>
+        <v>147.628</v>
       </c>
       <c r="G69">
         <v>11</v>
@@ -6945,28 +6945,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M69">
-        <v>8.043772100000002</v>
+        <v>8.163828400000002</v>
       </c>
       <c r="N69">
-        <v>29.48956123333333</v>
+        <v>29.36950493333333</v>
       </c>
       <c r="O69">
-        <v>6.487703471333332</v>
+        <v>6.461291085333333</v>
       </c>
       <c r="P69">
-        <v>23.001857762</v>
+        <v>22.908213848</v>
       </c>
       <c r="Q69">
-        <v>28.801857762</v>
+        <v>28.708213848</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2311321455506692</v>
+        <v>0.2364306103029534</v>
       </c>
       <c r="T69">
-        <v>2.415499145747702</v>
+        <v>2.484555903521101</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.66613584605826</v>
+        <v>4.597516201263286</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1049889152969451</v>
+        <v>0.1048044425621694</v>
       </c>
       <c r="C70">
-        <v>115.4395928834291</v>
+        <v>114.0566623268197</v>
       </c>
       <c r="D70">
-        <v>252.0675928834292</v>
+        <v>252.8556623268197</v>
       </c>
       <c r="E70">
-        <v>-12.27199999999999</v>
+        <v>-10.10099999999997</v>
       </c>
       <c r="F70">
-        <v>147.628</v>
+        <v>149.799</v>
       </c>
       <c r="G70">
         <v>11</v>
@@ -7027,28 +7027,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M70">
-        <v>8.163828400000002</v>
+        <v>8.283884700000002</v>
       </c>
       <c r="N70">
-        <v>29.36950493333333</v>
+        <v>29.24944863333333</v>
       </c>
       <c r="O70">
-        <v>6.461291085333333</v>
+        <v>6.434878699333333</v>
       </c>
       <c r="P70">
-        <v>22.908213848</v>
+        <v>22.814569934</v>
       </c>
       <c r="Q70">
-        <v>28.708213848</v>
+        <v>28.614569934</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2364306103029534</v>
+        <v>0.2420709114908689</v>
       </c>
       <c r="T70">
-        <v>2.484555903521101</v>
+        <v>2.558067935989559</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.597516201263286</v>
+        <v>4.530885531679759</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1048044425621694</v>
+        <v>0.1059849698273936</v>
       </c>
       <c r="C71">
-        <v>114.0566623268197</v>
+        <v>106.9259023668291</v>
       </c>
       <c r="D71">
-        <v>252.8556623268197</v>
+        <v>247.8959023668291</v>
       </c>
       <c r="E71">
-        <v>-10.10099999999997</v>
+        <v>-7.929999999999978</v>
       </c>
       <c r="F71">
-        <v>149.799</v>
+        <v>151.97</v>
       </c>
       <c r="G71">
         <v>11</v>
@@ -7109,45 +7109,45 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M71">
-        <v>8.283884700000002</v>
+        <v>8.783866000000002</v>
       </c>
       <c r="N71">
-        <v>29.24944863333333</v>
+        <v>28.74946733333333</v>
       </c>
       <c r="O71">
-        <v>6.434878699333333</v>
+        <v>6.324882813333332</v>
       </c>
       <c r="P71">
-        <v>22.814569934</v>
+        <v>22.42458452</v>
       </c>
       <c r="Q71">
-        <v>28.614569934</v>
+        <v>28.22458452</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2420709114908689</v>
+        <v>0.2480872327579788</v>
       </c>
       <c r="T71">
-        <v>2.558067935989559</v>
+        <v>2.63648077062258</v>
       </c>
       <c r="U71">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V71">
         <v>0.22</v>
       </c>
       <c r="W71">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y71">
-        <v>4.530885531679759</v>
+        <v>4.272985645879995</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1059849698273936</v>
+        <v>0.1058199970926179</v>
       </c>
       <c r="C72">
-        <v>106.9259023668291</v>
+        <v>105.4362763577348</v>
       </c>
       <c r="D72">
-        <v>247.8959023668291</v>
+        <v>248.5772763577348</v>
       </c>
       <c r="E72">
-        <v>-7.929999999999978</v>
+        <v>-5.758999999999986</v>
       </c>
       <c r="F72">
-        <v>151.97</v>
+        <v>154.141</v>
       </c>
       <c r="G72">
         <v>11</v>
@@ -7191,28 +7191,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M72">
-        <v>8.783866000000002</v>
+        <v>8.909349800000001</v>
       </c>
       <c r="N72">
-        <v>28.74946733333333</v>
+        <v>28.62398353333333</v>
       </c>
       <c r="O72">
-        <v>6.324882813333332</v>
+        <v>6.297276377333333</v>
       </c>
       <c r="P72">
-        <v>22.42458452</v>
+        <v>22.326707156</v>
       </c>
       <c r="Q72">
-        <v>28.22458452</v>
+        <v>28.126707156</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2480872327579788</v>
+        <v>0.2545184727331652</v>
       </c>
       <c r="T72">
-        <v>2.63648077062258</v>
+        <v>2.72030138695443</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.272985645879995</v>
+        <v>4.21280274945915</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1058199970926179</v>
+        <v>0.1056550243578422</v>
       </c>
       <c r="C73">
-        <v>105.4362763577349</v>
+        <v>103.9504063618373</v>
       </c>
       <c r="D73">
-        <v>248.5772763577349</v>
+        <v>249.2624063618373</v>
       </c>
       <c r="E73">
-        <v>-5.758999999999986</v>
+        <v>-3.587999999999994</v>
       </c>
       <c r="F73">
-        <v>154.141</v>
+        <v>156.312</v>
       </c>
       <c r="G73">
         <v>11</v>
@@ -7273,28 +7273,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M73">
-        <v>8.909349800000001</v>
+        <v>9.034833600000001</v>
       </c>
       <c r="N73">
-        <v>28.62398353333333</v>
+        <v>28.49849973333333</v>
       </c>
       <c r="O73">
-        <v>6.297276377333333</v>
+        <v>6.269669941333333</v>
       </c>
       <c r="P73">
-        <v>22.326707156</v>
+        <v>22.228829792</v>
       </c>
       <c r="Q73">
-        <v>28.126707156</v>
+        <v>28.028829792</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2545184727331651</v>
+        <v>0.2614090869922935</v>
       </c>
       <c r="T73">
-        <v>2.720301386954429</v>
+        <v>2.810109190167126</v>
       </c>
       <c r="U73">
         <v>0.0578</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.21280274945915</v>
+        <v>4.154291600161106</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1056550243578422</v>
+        <v>0.1054900516230664</v>
       </c>
       <c r="C74">
-        <v>103.9504063618373</v>
+        <v>102.4683235220028</v>
       </c>
       <c r="D74">
-        <v>249.2624063618373</v>
+        <v>249.9513235220028</v>
       </c>
       <c r="E74">
-        <v>-3.587999999999994</v>
+        <v>-1.417000000000002</v>
       </c>
       <c r="F74">
-        <v>156.312</v>
+        <v>158.483</v>
       </c>
       <c r="G74">
         <v>11</v>
@@ -7355,28 +7355,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M74">
-        <v>9.034833600000001</v>
+        <v>9.1603174</v>
       </c>
       <c r="N74">
-        <v>28.49849973333333</v>
+        <v>28.37301593333333</v>
       </c>
       <c r="O74">
-        <v>6.269669941333333</v>
+        <v>6.242063505333333</v>
       </c>
       <c r="P74">
-        <v>22.228829792</v>
+        <v>22.130952428</v>
       </c>
       <c r="Q74">
-        <v>28.028829792</v>
+        <v>27.930952428</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2614090869922935</v>
+        <v>0.2688101171224683</v>
       </c>
       <c r="T74">
-        <v>2.810109190167126</v>
+        <v>2.906569423247429</v>
       </c>
       <c r="U74">
         <v>0.0578</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.154291600161106</v>
+        <v>4.097383496049311</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1054900516230664</v>
+        <v>0.1053250788882907</v>
       </c>
       <c r="C75">
-        <v>102.4683235220028</v>
+        <v>100.9900593263453</v>
       </c>
       <c r="D75">
-        <v>249.9513235220028</v>
+        <v>250.6440593263454</v>
       </c>
       <c r="E75">
-        <v>-1.417000000000002</v>
+        <v>0.7540000000000191</v>
       </c>
       <c r="F75">
-        <v>158.483</v>
+        <v>160.654</v>
       </c>
       <c r="G75">
         <v>11</v>
@@ -7437,28 +7437,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M75">
-        <v>9.1603174</v>
+        <v>9.285801200000002</v>
       </c>
       <c r="N75">
-        <v>28.37301593333333</v>
+        <v>28.24753213333333</v>
       </c>
       <c r="O75">
-        <v>6.242063505333333</v>
+        <v>6.214457069333332</v>
       </c>
       <c r="P75">
-        <v>22.130952428</v>
+        <v>22.033075064</v>
       </c>
       <c r="Q75">
-        <v>27.930952428</v>
+        <v>27.833075064</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2688101171224683</v>
+        <v>0.2767804572626565</v>
       </c>
       <c r="T75">
-        <v>2.906569423247429</v>
+        <v>3.010449674256988</v>
       </c>
       <c r="U75">
         <v>0.0578</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.097383496049311</v>
+        <v>4.042013448805401</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1053250788882907</v>
+        <v>0.107207606153515</v>
       </c>
       <c r="C76">
-        <v>100.9900593263453</v>
+        <v>91.13525099861553</v>
       </c>
       <c r="D76">
-        <v>250.6440593263454</v>
+        <v>242.9602509986155</v>
       </c>
       <c r="E76">
-        <v>0.7540000000000191</v>
+        <v>2.925000000000011</v>
       </c>
       <c r="F76">
-        <v>160.654</v>
+        <v>162.825</v>
       </c>
       <c r="G76">
         <v>11</v>
@@ -7519,45 +7519,45 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M76">
-        <v>9.285801200000002</v>
+        <v>9.981172500000001</v>
       </c>
       <c r="N76">
-        <v>28.24753213333333</v>
+        <v>27.55216083333333</v>
       </c>
       <c r="O76">
-        <v>6.214457069333332</v>
+        <v>6.061475383333333</v>
       </c>
       <c r="P76">
-        <v>22.033075064</v>
+        <v>21.49068545</v>
       </c>
       <c r="Q76">
-        <v>27.833075064</v>
+        <v>27.29068545</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2767804572626565</v>
+        <v>0.2853884246140599</v>
       </c>
       <c r="T76">
-        <v>3.010449674256988</v>
+        <v>3.12264034534731</v>
       </c>
       <c r="U76">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V76">
         <v>0.22</v>
       </c>
       <c r="W76">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y76">
-        <v>4.042013448805401</v>
+        <v>3.760413251382373</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.107207606153515</v>
+        <v>0.1070699334187393</v>
       </c>
       <c r="C77">
-        <v>91.13525099861553</v>
+        <v>89.51017948801291</v>
       </c>
       <c r="D77">
-        <v>242.9602509986155</v>
+        <v>243.5061794880129</v>
       </c>
       <c r="E77">
-        <v>2.925000000000011</v>
+        <v>5.096000000000004</v>
       </c>
       <c r="F77">
-        <v>162.825</v>
+        <v>164.996</v>
       </c>
       <c r="G77">
         <v>11</v>
@@ -7601,28 +7601,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M77">
-        <v>9.981172500000001</v>
+        <v>10.1142548</v>
       </c>
       <c r="N77">
-        <v>27.55216083333333</v>
+        <v>27.41907853333333</v>
       </c>
       <c r="O77">
-        <v>6.061475383333333</v>
+        <v>6.032197277333332</v>
       </c>
       <c r="P77">
-        <v>21.49068545</v>
+        <v>21.386881256</v>
       </c>
       <c r="Q77">
-        <v>27.29068545</v>
+        <v>27.186881256</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2853884246140599</v>
+        <v>0.2947137225780803</v>
       </c>
       <c r="T77">
-        <v>3.12264034534731</v>
+        <v>3.244180239028493</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.760413251382373</v>
+        <v>3.710934129653658</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1070699334187393</v>
+        <v>0.1069322606839635</v>
       </c>
       <c r="C78">
-        <v>89.51017948801291</v>
+        <v>87.88756689083149</v>
       </c>
       <c r="D78">
-        <v>243.5061794880129</v>
+        <v>244.0545668908315</v>
       </c>
       <c r="E78">
-        <v>5.096000000000004</v>
+        <v>7.267000000000024</v>
       </c>
       <c r="F78">
-        <v>164.996</v>
+        <v>167.167</v>
       </c>
       <c r="G78">
         <v>11</v>
@@ -7683,28 +7683,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M78">
-        <v>10.1142548</v>
+        <v>10.2473371</v>
       </c>
       <c r="N78">
-        <v>27.41907853333333</v>
+        <v>27.28599623333333</v>
       </c>
       <c r="O78">
-        <v>6.032197277333332</v>
+        <v>6.002919171333333</v>
       </c>
       <c r="P78">
-        <v>21.386881256</v>
+        <v>21.283077062</v>
       </c>
       <c r="Q78">
-        <v>27.186881256</v>
+        <v>27.083077062</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2947137225780803</v>
+        <v>0.3048499160172327</v>
       </c>
       <c r="T78">
-        <v>3.244180239028493</v>
+        <v>3.376288819116735</v>
       </c>
       <c r="U78">
         <v>0.0613</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.710934129653658</v>
+        <v>3.662740179917896</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1069322606839635</v>
+        <v>0.1067945879491878</v>
       </c>
       <c r="C79">
-        <v>87.88756689083149</v>
+        <v>86.26742985733526</v>
       </c>
       <c r="D79">
-        <v>244.0545668908315</v>
+        <v>244.6054298573353</v>
       </c>
       <c r="E79">
-        <v>7.267000000000024</v>
+        <v>9.438000000000017</v>
       </c>
       <c r="F79">
-        <v>167.167</v>
+        <v>169.338</v>
       </c>
       <c r="G79">
         <v>11</v>
@@ -7765,28 +7765,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M79">
-        <v>10.2473371</v>
+        <v>10.3804194</v>
       </c>
       <c r="N79">
-        <v>27.28599623333333</v>
+        <v>27.15291393333333</v>
       </c>
       <c r="O79">
-        <v>6.002919171333333</v>
+        <v>5.973641065333333</v>
       </c>
       <c r="P79">
-        <v>21.283077062</v>
+        <v>21.179272868</v>
       </c>
       <c r="Q79">
-        <v>27.083077062</v>
+        <v>26.979272868</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3048499160172327</v>
+        <v>0.3159075815872173</v>
       </c>
       <c r="T79">
-        <v>3.376288819116735</v>
+        <v>3.520407270122091</v>
       </c>
       <c r="U79">
         <v>0.0613</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.662740179917896</v>
+        <v>3.615781972483051</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1067945879491878</v>
+        <v>0.1066569152144121</v>
       </c>
       <c r="C80">
-        <v>86.26742985733526</v>
+        <v>84.64978518845601</v>
       </c>
       <c r="D80">
-        <v>244.6054298573353</v>
+        <v>245.158785188456</v>
       </c>
       <c r="E80">
-        <v>9.438000000000017</v>
+        <v>11.60900000000001</v>
       </c>
       <c r="F80">
-        <v>169.338</v>
+        <v>171.509</v>
       </c>
       <c r="G80">
         <v>11</v>
@@ -7847,28 +7847,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M80">
-        <v>10.3804194</v>
+        <v>10.5135017</v>
       </c>
       <c r="N80">
-        <v>27.15291393333333</v>
+        <v>27.01983163333333</v>
       </c>
       <c r="O80">
-        <v>5.973641065333333</v>
+        <v>5.944362959333334</v>
       </c>
       <c r="P80">
-        <v>21.179272868</v>
+        <v>21.075468674</v>
       </c>
       <c r="Q80">
-        <v>26.979272868</v>
+        <v>26.875468674</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3159075815872173</v>
+        <v>0.328018358163867</v>
       </c>
       <c r="T80">
-        <v>3.520407270122091</v>
+        <v>3.67825128788986</v>
       </c>
       <c r="U80">
         <v>0.0613</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.615781972483051</v>
+        <v>3.570012580426304</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1066569152144121</v>
+        <v>0.1065192424796363</v>
       </c>
       <c r="C81">
-        <v>84.64978518845601</v>
+        <v>83.03464983750038</v>
       </c>
       <c r="D81">
-        <v>245.158785188456</v>
+        <v>245.7146498375004</v>
       </c>
       <c r="E81">
-        <v>11.60900000000001</v>
+        <v>13.78000000000003</v>
       </c>
       <c r="F81">
-        <v>171.509</v>
+        <v>173.68</v>
       </c>
       <c r="G81">
         <v>11</v>
@@ -7929,28 +7929,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M81">
-        <v>10.5135017</v>
+        <v>10.646584</v>
       </c>
       <c r="N81">
-        <v>27.01983163333333</v>
+        <v>26.88674933333333</v>
       </c>
       <c r="O81">
-        <v>5.944362959333334</v>
+        <v>5.915084853333332</v>
       </c>
       <c r="P81">
-        <v>21.075468674</v>
+        <v>20.97166447999999</v>
       </c>
       <c r="Q81">
-        <v>26.875468674</v>
+        <v>26.77166447999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.328018358163867</v>
+        <v>0.3413402123981818</v>
       </c>
       <c r="T81">
-        <v>3.67825128788986</v>
+        <v>3.851879707434407</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.570012580426304</v>
+        <v>3.525387423170974</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1065192424796363</v>
+        <v>0.1081506097448606</v>
       </c>
       <c r="C82">
-        <v>83.03464983750038</v>
+        <v>74.43466962429591</v>
       </c>
       <c r="D82">
-        <v>245.7146498375004</v>
+        <v>239.2856696242959</v>
       </c>
       <c r="E82">
-        <v>13.78000000000003</v>
+        <v>15.95100000000002</v>
       </c>
       <c r="F82">
-        <v>173.68</v>
+        <v>175.851</v>
       </c>
       <c r="G82">
         <v>11</v>
@@ -8011,45 +8011,45 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M82">
-        <v>10.646584</v>
+        <v>11.2720491</v>
       </c>
       <c r="N82">
-        <v>26.88674933333333</v>
+        <v>26.26128423333333</v>
       </c>
       <c r="O82">
-        <v>5.915084853333332</v>
+        <v>5.777482531333332</v>
       </c>
       <c r="P82">
-        <v>20.97166447999999</v>
+        <v>20.48380170199999</v>
       </c>
       <c r="Q82">
-        <v>26.77166447999999</v>
+        <v>26.28380170199999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3413402123981818</v>
+        <v>0.3560643670782138</v>
       </c>
       <c r="T82">
-        <v>3.851879707434407</v>
+        <v>4.043784802720485</v>
       </c>
       <c r="U82">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V82">
         <v>0.22</v>
       </c>
       <c r="W82">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y82">
-        <v>3.525387423170974</v>
+        <v>3.329770213060314</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1081506097448606</v>
+        <v>0.1080347770100849</v>
       </c>
       <c r="C83">
-        <v>74.43466962429591</v>
+        <v>72.7090333716543</v>
       </c>
       <c r="D83">
-        <v>239.2856696242959</v>
+        <v>239.7310333716543</v>
       </c>
       <c r="E83">
-        <v>15.95100000000002</v>
+        <v>18.12200000000001</v>
       </c>
       <c r="F83">
-        <v>175.851</v>
+        <v>178.022</v>
       </c>
       <c r="G83">
         <v>11</v>
@@ -8093,28 +8093,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M83">
-        <v>11.2720491</v>
+        <v>11.4112102</v>
       </c>
       <c r="N83">
-        <v>26.26128423333333</v>
+        <v>26.12212313333333</v>
       </c>
       <c r="O83">
-        <v>5.777482531333332</v>
+        <v>5.746867089333333</v>
       </c>
       <c r="P83">
-        <v>20.48380170199999</v>
+        <v>20.375256044</v>
       </c>
       <c r="Q83">
-        <v>26.28380170199999</v>
+        <v>26.175256044</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3560643670782138</v>
+        <v>0.3724245389449161</v>
       </c>
       <c r="T83">
-        <v>4.043784802720485</v>
+        <v>4.257012686371684</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.329770213060314</v>
+        <v>3.289163259242506</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1080347770100849</v>
+        <v>0.1079189442753092</v>
       </c>
       <c r="C84">
-        <v>72.7090333716543</v>
+        <v>70.98505805196729</v>
       </c>
       <c r="D84">
-        <v>239.7310333716543</v>
+        <v>240.1780580519673</v>
       </c>
       <c r="E84">
-        <v>18.12200000000001</v>
+        <v>20.29300000000003</v>
       </c>
       <c r="F84">
-        <v>178.022</v>
+        <v>180.193</v>
       </c>
       <c r="G84">
         <v>11</v>
@@ -8175,28 +8175,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M84">
-        <v>11.4112102</v>
+        <v>11.5503713</v>
       </c>
       <c r="N84">
-        <v>26.12212313333333</v>
+        <v>25.98296203333333</v>
       </c>
       <c r="O84">
-        <v>5.746867089333333</v>
+        <v>5.716251647333332</v>
       </c>
       <c r="P84">
-        <v>20.375256044</v>
+        <v>20.266710386</v>
       </c>
       <c r="Q84">
-        <v>26.175256044</v>
+        <v>26.066710386</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3724245389449161</v>
+        <v>0.3907094369135834</v>
       </c>
       <c r="T84">
-        <v>4.257012686371684</v>
+        <v>4.495326203393611</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.289163259242506</v>
+        <v>3.249534786239584</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1079189442753092</v>
+        <v>0.1078031115405335</v>
       </c>
       <c r="C85">
-        <v>70.98505805196729</v>
+        <v>69.26275297398081</v>
       </c>
       <c r="D85">
-        <v>240.1780580519673</v>
+        <v>240.6267529739808</v>
       </c>
       <c r="E85">
-        <v>20.29300000000003</v>
+        <v>22.46400000000003</v>
       </c>
       <c r="F85">
-        <v>180.193</v>
+        <v>182.364</v>
       </c>
       <c r="G85">
         <v>11</v>
@@ -8257,28 +8257,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M85">
-        <v>11.5503713</v>
+        <v>11.6895324</v>
       </c>
       <c r="N85">
-        <v>25.98296203333333</v>
+        <v>25.84380093333333</v>
       </c>
       <c r="O85">
-        <v>5.716251647333332</v>
+        <v>5.685636205333332</v>
       </c>
       <c r="P85">
-        <v>20.266710386</v>
+        <v>20.158164728</v>
       </c>
       <c r="Q85">
-        <v>26.066710386</v>
+        <v>25.958164728</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3907094369135834</v>
+        <v>0.4112799471283342</v>
       </c>
       <c r="T85">
-        <v>4.495326203393611</v>
+        <v>4.76342891004328</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.249534786239584</v>
+        <v>3.21084984830816</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1078031115405334</v>
+        <v>0.1076872788057577</v>
       </c>
       <c r="C86">
-        <v>69.26275297398092</v>
+        <v>67.54212751613292</v>
       </c>
       <c r="D86">
-        <v>240.6267529739809</v>
+        <v>241.0771275161329</v>
       </c>
       <c r="E86">
-        <v>22.464</v>
+        <v>24.63500000000002</v>
       </c>
       <c r="F86">
-        <v>182.364</v>
+        <v>184.535</v>
       </c>
       <c r="G86">
         <v>11</v>
@@ -8339,28 +8339,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M86">
-        <v>11.6895324</v>
+        <v>11.8286935</v>
       </c>
       <c r="N86">
-        <v>25.84380093333333</v>
+        <v>25.70463983333333</v>
       </c>
       <c r="O86">
-        <v>5.685636205333333</v>
+        <v>5.655020763333333</v>
       </c>
       <c r="P86">
-        <v>20.158164728</v>
+        <v>20.04961907</v>
       </c>
       <c r="Q86">
-        <v>25.958164728</v>
+        <v>25.84961907</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4112799471283339</v>
+        <v>0.4345931920383847</v>
       </c>
       <c r="T86">
-        <v>4.763428910043277</v>
+        <v>5.067278644246234</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.210849848308161</v>
+        <v>3.173075144210417</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1076872788057577</v>
+        <v>0.107571446070982</v>
       </c>
       <c r="C87">
-        <v>67.54212751613292</v>
+        <v>65.82319112720629</v>
       </c>
       <c r="D87">
-        <v>241.0771275161329</v>
+        <v>241.5291911272063</v>
       </c>
       <c r="E87">
-        <v>24.63500000000002</v>
+        <v>26.80600000000001</v>
       </c>
       <c r="F87">
-        <v>184.535</v>
+        <v>186.706</v>
       </c>
       <c r="G87">
         <v>11</v>
@@ -8421,28 +8421,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M87">
-        <v>11.8286935</v>
+        <v>11.9678546</v>
       </c>
       <c r="N87">
-        <v>25.70463983333333</v>
+        <v>25.56547873333333</v>
       </c>
       <c r="O87">
-        <v>5.655020763333333</v>
+        <v>5.624405321333333</v>
       </c>
       <c r="P87">
-        <v>20.04961907</v>
+        <v>19.94107341199999</v>
       </c>
       <c r="Q87">
-        <v>25.84961907</v>
+        <v>25.741073412</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4345931920383847</v>
+        <v>0.4612369005070141</v>
       </c>
       <c r="T87">
-        <v>5.067278644246234</v>
+        <v>5.414535483335327</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.173075144210417</v>
+        <v>3.136178921603319</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.107571446070982</v>
+        <v>0.1074556133362063</v>
       </c>
       <c r="C88">
-        <v>65.82319112720629</v>
+        <v>64.10595332698972</v>
       </c>
       <c r="D88">
-        <v>241.5291911272063</v>
+        <v>241.9829533269897</v>
       </c>
       <c r="E88">
-        <v>26.80600000000001</v>
+        <v>28.977</v>
       </c>
       <c r="F88">
-        <v>186.706</v>
+        <v>188.877</v>
       </c>
       <c r="G88">
         <v>11</v>
@@ -8503,28 +8503,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M88">
-        <v>11.9678546</v>
+        <v>12.1070157</v>
       </c>
       <c r="N88">
-        <v>25.56547873333333</v>
+        <v>25.42631763333333</v>
       </c>
       <c r="O88">
-        <v>5.624405321333333</v>
+        <v>5.593789879333332</v>
       </c>
       <c r="P88">
-        <v>19.94107341199999</v>
+        <v>19.832527754</v>
       </c>
       <c r="Q88">
-        <v>25.741073412</v>
+        <v>25.632527754</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4612369005070141</v>
+        <v>0.4919796410477403</v>
       </c>
       <c r="T88">
-        <v>5.414535483335327</v>
+        <v>5.815216451515051</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.136178921603319</v>
+        <v>3.100130888021672</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1074556133362063</v>
+        <v>0.1073397806014305</v>
       </c>
       <c r="C89">
-        <v>64.10595332698972</v>
+        <v>62.39042370694619</v>
       </c>
       <c r="D89">
-        <v>241.9829533269897</v>
+        <v>242.4384237069462</v>
       </c>
       <c r="E89">
-        <v>28.977</v>
+        <v>31.14800000000002</v>
       </c>
       <c r="F89">
-        <v>188.877</v>
+        <v>191.048</v>
       </c>
       <c r="G89">
         <v>11</v>
@@ -8585,28 +8585,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M89">
-        <v>12.1070157</v>
+        <v>12.2461768</v>
       </c>
       <c r="N89">
-        <v>25.42631763333333</v>
+        <v>25.28715653333333</v>
       </c>
       <c r="O89">
-        <v>5.593789879333332</v>
+        <v>5.563174437333333</v>
       </c>
       <c r="P89">
-        <v>19.832527754</v>
+        <v>19.723982096</v>
       </c>
       <c r="Q89">
-        <v>25.632527754</v>
+        <v>25.523982096</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4919796410477403</v>
+        <v>0.5278461716785877</v>
       </c>
       <c r="T89">
-        <v>5.815216451515051</v>
+        <v>6.282677581058062</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.100130888021672</v>
+        <v>3.064902127930517</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1073397806014305</v>
+        <v>0.1072239478666548</v>
       </c>
       <c r="C90">
-        <v>62.39042370694619</v>
+        <v>60.67661193088875</v>
       </c>
       <c r="D90">
-        <v>242.4384237069462</v>
+        <v>242.8956119308888</v>
       </c>
       <c r="E90">
-        <v>31.14800000000002</v>
+        <v>33.31900000000002</v>
       </c>
       <c r="F90">
-        <v>191.048</v>
+        <v>193.219</v>
       </c>
       <c r="G90">
         <v>11</v>
@@ -8667,28 +8667,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M90">
-        <v>12.2461768</v>
+        <v>12.3853379</v>
       </c>
       <c r="N90">
-        <v>25.28715653333333</v>
+        <v>25.14799543333333</v>
       </c>
       <c r="O90">
-        <v>5.563174437333333</v>
+        <v>5.532558995333332</v>
       </c>
       <c r="P90">
-        <v>19.723982096</v>
+        <v>19.615436438</v>
       </c>
       <c r="Q90">
-        <v>25.523982096</v>
+        <v>25.415436438</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5278461716785877</v>
+        <v>0.5702338896968617</v>
       </c>
       <c r="T90">
-        <v>6.282677581058062</v>
+        <v>6.835131643245256</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.064902127930517</v>
+        <v>3.0304650253695</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1072239478666548</v>
+        <v>0.1125837151318791</v>
       </c>
       <c r="C91">
-        <v>60.67661193088875</v>
+        <v>39.01187835941883</v>
       </c>
       <c r="D91">
-        <v>242.8956119308888</v>
+        <v>223.4018783594188</v>
       </c>
       <c r="E91">
-        <v>33.31900000000002</v>
+        <v>35.49000000000001</v>
       </c>
       <c r="F91">
-        <v>193.219</v>
+        <v>195.39</v>
       </c>
       <c r="G91">
         <v>11</v>
@@ -8749,45 +8749,45 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M91">
-        <v>12.3853379</v>
+        <v>14.048541</v>
       </c>
       <c r="N91">
-        <v>25.14799543333333</v>
+        <v>23.48479233333333</v>
       </c>
       <c r="O91">
-        <v>5.532558995333332</v>
+        <v>5.166654313333333</v>
       </c>
       <c r="P91">
-        <v>19.615436438</v>
+        <v>18.31813802</v>
       </c>
       <c r="Q91">
-        <v>25.415436438</v>
+        <v>24.11813802</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5702338896968617</v>
+        <v>0.6210991513187907</v>
       </c>
       <c r="T91">
-        <v>6.835131643245256</v>
+        <v>7.498076517869889</v>
       </c>
       <c r="U91">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V91">
         <v>0.22</v>
       </c>
       <c r="W91">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y91">
-        <v>3.0304650253695</v>
+        <v>2.671689062468005</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1125837151318791</v>
+        <v>0.1125287223971033</v>
       </c>
       <c r="C92">
-        <v>39.01187835941883</v>
+        <v>37.02498918611661</v>
       </c>
       <c r="D92">
-        <v>223.4018783594188</v>
+        <v>223.5859891861166</v>
       </c>
       <c r="E92">
-        <v>35.49000000000001</v>
+        <v>37.66100000000003</v>
       </c>
       <c r="F92">
-        <v>195.39</v>
+        <v>197.561</v>
       </c>
       <c r="G92">
         <v>11</v>
@@ -8831,28 +8831,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M92">
-        <v>14.048541</v>
+        <v>14.2046359</v>
       </c>
       <c r="N92">
-        <v>23.48479233333333</v>
+        <v>23.32869743333333</v>
       </c>
       <c r="O92">
-        <v>5.166654313333333</v>
+        <v>5.132313435333332</v>
       </c>
       <c r="P92">
-        <v>18.31813802</v>
+        <v>18.19638399799999</v>
       </c>
       <c r="Q92">
-        <v>24.11813802</v>
+        <v>23.996383998</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6210991513187907</v>
+        <v>0.6832678044122594</v>
       </c>
       <c r="T92">
-        <v>7.498076517869889</v>
+        <v>8.308342475744443</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.671689062468005</v>
+        <v>2.642329842001323</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1125287223971033</v>
+        <v>0.1124737296623276</v>
       </c>
       <c r="C93">
-        <v>37.02498918611661</v>
+        <v>35.03840372337362</v>
       </c>
       <c r="D93">
-        <v>223.5859891861166</v>
+        <v>223.7704037233736</v>
       </c>
       <c r="E93">
-        <v>37.66100000000003</v>
+        <v>39.83200000000002</v>
       </c>
       <c r="F93">
-        <v>197.561</v>
+        <v>199.732</v>
       </c>
       <c r="G93">
         <v>11</v>
@@ -8913,28 +8913,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M93">
-        <v>14.2046359</v>
+        <v>14.3607308</v>
       </c>
       <c r="N93">
-        <v>23.32869743333333</v>
+        <v>23.17260253333333</v>
       </c>
       <c r="O93">
-        <v>5.132313435333332</v>
+        <v>5.097972557333333</v>
       </c>
       <c r="P93">
-        <v>18.19638399799999</v>
+        <v>18.074629976</v>
       </c>
       <c r="Q93">
-        <v>23.996383998</v>
+        <v>23.874629976</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6832678044122594</v>
+        <v>0.7609786207790955</v>
       </c>
       <c r="T93">
-        <v>8.308342475744443</v>
+        <v>9.321174923087636</v>
       </c>
       <c r="U93">
         <v>0.07190000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.642329842001323</v>
+        <v>2.613608865457831</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1124737296623276</v>
+        <v>0.1124187369275519</v>
       </c>
       <c r="C94">
-        <v>35.03840372337362</v>
+        <v>33.05212272331508</v>
       </c>
       <c r="D94">
-        <v>223.7704037233736</v>
+        <v>223.9551227233151</v>
       </c>
       <c r="E94">
-        <v>39.83200000000002</v>
+        <v>42.00300000000001</v>
       </c>
       <c r="F94">
-        <v>199.732</v>
+        <v>201.903</v>
       </c>
       <c r="G94">
         <v>11</v>
@@ -8995,28 +8995,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M94">
-        <v>14.3607308</v>
+        <v>14.5168257</v>
       </c>
       <c r="N94">
-        <v>23.17260253333333</v>
+        <v>23.01650763333333</v>
       </c>
       <c r="O94">
-        <v>5.097972557333333</v>
+        <v>5.063631679333333</v>
       </c>
       <c r="P94">
-        <v>18.074629976</v>
+        <v>17.952875954</v>
       </c>
       <c r="Q94">
-        <v>23.874629976</v>
+        <v>23.752875954</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7609786207790955</v>
+        <v>0.8608925275364558</v>
       </c>
       <c r="T94">
-        <v>9.321174923087636</v>
+        <v>10.62338806967174</v>
       </c>
       <c r="U94">
         <v>0.07190000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.613608865457831</v>
+        <v>2.585505544323876</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1124187369275519</v>
+        <v>0.1123637441927761</v>
       </c>
       <c r="C95">
-        <v>33.05212272331508</v>
+        <v>31.06614694055142</v>
       </c>
       <c r="D95">
-        <v>223.9551227233151</v>
+        <v>224.1401469405515</v>
       </c>
       <c r="E95">
-        <v>42.00300000000001</v>
+        <v>44.17400000000004</v>
       </c>
       <c r="F95">
-        <v>201.903</v>
+        <v>204.074</v>
       </c>
       <c r="G95">
         <v>11</v>
@@ -9077,28 +9077,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M95">
-        <v>14.5168257</v>
+        <v>14.6729206</v>
       </c>
       <c r="N95">
-        <v>23.01650763333333</v>
+        <v>22.86041273333333</v>
       </c>
       <c r="O95">
-        <v>5.063631679333333</v>
+        <v>5.029290801333332</v>
       </c>
       <c r="P95">
-        <v>17.952875954</v>
+        <v>17.83112193199999</v>
       </c>
       <c r="Q95">
-        <v>23.752875954</v>
+        <v>23.631121932</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8608925275364558</v>
+        <v>0.9941110698796034</v>
       </c>
       <c r="T95">
-        <v>10.62338806967174</v>
+        <v>12.35967226511721</v>
       </c>
       <c r="U95">
         <v>0.07190000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.585505544323876</v>
+        <v>2.55800016619277</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1123637441927761</v>
+        <v>0.1123087514580004</v>
       </c>
       <c r="C96">
-        <v>31.06614694055142</v>
+        <v>29.08047713218906</v>
       </c>
       <c r="D96">
-        <v>224.1401469405515</v>
+        <v>224.3254771321891</v>
       </c>
       <c r="E96">
-        <v>44.17400000000004</v>
+        <v>46.34500000000003</v>
       </c>
       <c r="F96">
-        <v>204.074</v>
+        <v>206.245</v>
       </c>
       <c r="G96">
         <v>11</v>
@@ -9159,28 +9159,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M96">
-        <v>14.6729206</v>
+        <v>14.8290155</v>
       </c>
       <c r="N96">
-        <v>22.86041273333333</v>
+        <v>22.70431783333333</v>
       </c>
       <c r="O96">
-        <v>5.029290801333332</v>
+        <v>4.994949923333332</v>
       </c>
       <c r="P96">
-        <v>17.83112193199999</v>
+        <v>17.70936791</v>
       </c>
       <c r="Q96">
-        <v>23.631121932</v>
+        <v>23.50936791</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9941110698796034</v>
+        <v>1.18061702916001</v>
       </c>
       <c r="T96">
-        <v>12.35967226511721</v>
+        <v>14.79047013874087</v>
       </c>
       <c r="U96">
         <v>0.07190000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.55800016619277</v>
+        <v>2.531073848653899</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1123087514580004</v>
+        <v>0.1122537587232247</v>
       </c>
       <c r="C97">
-        <v>29.08047713218906</v>
+        <v>27.09511405784062</v>
       </c>
       <c r="D97">
-        <v>224.3254771321891</v>
+        <v>224.5111140578406</v>
       </c>
       <c r="E97">
-        <v>46.34500000000003</v>
+        <v>48.51600000000002</v>
       </c>
       <c r="F97">
-        <v>206.245</v>
+        <v>208.416</v>
       </c>
       <c r="G97">
         <v>11</v>
@@ -9241,28 +9241,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M97">
-        <v>14.8290155</v>
+        <v>14.9851104</v>
       </c>
       <c r="N97">
-        <v>22.70431783333333</v>
+        <v>22.54822293333333</v>
       </c>
       <c r="O97">
-        <v>4.994949923333332</v>
+        <v>4.960609045333332</v>
       </c>
       <c r="P97">
-        <v>17.70936791</v>
+        <v>17.587613888</v>
       </c>
       <c r="Q97">
-        <v>23.50936791</v>
+        <v>23.387613888</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.18061702916001</v>
+        <v>1.46037596808062</v>
       </c>
       <c r="T97">
-        <v>14.79047013874087</v>
+        <v>18.43666694917637</v>
       </c>
       <c r="U97">
         <v>0.07190000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.531073848653899</v>
+        <v>2.504708496063754</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1122537587232247</v>
+        <v>0.115149505988449</v>
       </c>
       <c r="C98">
-        <v>27.09511405784062</v>
+        <v>15.54946264138016</v>
       </c>
       <c r="D98">
-        <v>224.5111140578406</v>
+        <v>215.1364626413802</v>
       </c>
       <c r="E98">
-        <v>48.51600000000002</v>
+        <v>50.68700000000001</v>
       </c>
       <c r="F98">
-        <v>208.416</v>
+        <v>210.587</v>
       </c>
       <c r="G98">
         <v>11</v>
@@ -9323,45 +9323,45 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M98">
-        <v>14.9851104</v>
+        <v>15.9624946</v>
       </c>
       <c r="N98">
-        <v>22.54822293333333</v>
+        <v>21.57083873333333</v>
       </c>
       <c r="O98">
-        <v>4.960609045333332</v>
+        <v>4.745584521333332</v>
       </c>
       <c r="P98">
-        <v>17.587613888</v>
+        <v>16.825254212</v>
       </c>
       <c r="Q98">
-        <v>23.387613888</v>
+        <v>22.625254212</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.460375968080616</v>
+        <v>1.926640866281631</v>
       </c>
       <c r="T98">
-        <v>18.43666694917632</v>
+        <v>24.51366163323545</v>
       </c>
       <c r="U98">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V98">
         <v>0.22</v>
       </c>
       <c r="W98">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y98">
-        <v>2.504708496063754</v>
+        <v>2.35134509197161</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.115149505988449</v>
+        <v>0.1151249332536733</v>
       </c>
       <c r="C99">
-        <v>15.54946264138016</v>
+        <v>13.45471935002683</v>
       </c>
       <c r="D99">
-        <v>215.1364626413802</v>
+        <v>215.2127193500268</v>
       </c>
       <c r="E99">
-        <v>50.68700000000001</v>
+        <v>52.858</v>
       </c>
       <c r="F99">
-        <v>210.587</v>
+        <v>212.758</v>
       </c>
       <c r="G99">
         <v>11</v>
@@ -9405,28 +9405,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M99">
-        <v>15.9624946</v>
+        <v>16.1270564</v>
       </c>
       <c r="N99">
-        <v>21.57083873333333</v>
+        <v>21.40627693333333</v>
       </c>
       <c r="O99">
-        <v>4.745584521333332</v>
+        <v>4.709380925333333</v>
       </c>
       <c r="P99">
-        <v>16.825254212</v>
+        <v>16.696896008</v>
       </c>
       <c r="Q99">
-        <v>22.625254212</v>
+        <v>22.496896008</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.926640866281631</v>
+        <v>2.85917066268366</v>
       </c>
       <c r="T99">
-        <v>24.51366163323545</v>
+        <v>36.66765100135372</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.35134509197161</v>
+        <v>2.327351774706594</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1151249332536733</v>
+        <v>0.1151003605188975</v>
       </c>
       <c r="C100">
-        <v>13.45471935002683</v>
+        <v>11.36003013734961</v>
       </c>
       <c r="D100">
-        <v>215.2127193500268</v>
+        <v>215.2890301373496</v>
       </c>
       <c r="E100">
-        <v>52.858</v>
+        <v>55.02900000000002</v>
       </c>
       <c r="F100">
-        <v>212.758</v>
+        <v>214.929</v>
       </c>
       <c r="G100">
         <v>11</v>
@@ -9487,28 +9487,28 @@
         <v>37.53333333333333</v>
       </c>
       <c r="M100">
-        <v>16.1270564</v>
+        <v>16.2916182</v>
       </c>
       <c r="N100">
-        <v>21.40627693333333</v>
+        <v>21.24171513333333</v>
       </c>
       <c r="O100">
-        <v>4.709380925333333</v>
+        <v>4.673177329333332</v>
       </c>
       <c r="P100">
-        <v>16.696896008</v>
+        <v>16.568537804</v>
       </c>
       <c r="Q100">
-        <v>22.496896008</v>
+        <v>22.368537804</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.85917066268366</v>
+        <v>5.656760051889747</v>
       </c>
       <c r="T100">
-        <v>36.66765100135372</v>
+        <v>73.12961910570851</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.327351774706594</v>
+        <v>2.303843170921678</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1151003605188975</v>
-      </c>
-      <c r="C101">
-        <v>11.36003013734961</v>
-      </c>
-      <c r="D101">
-        <v>215.2890301373496</v>
-      </c>
-      <c r="E101">
-        <v>55.02900000000002</v>
-      </c>
-      <c r="F101">
-        <v>214.929</v>
-      </c>
-      <c r="G101">
-        <v>11</v>
-      </c>
-      <c r="H101">
-        <v>57.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>43.33333333333334</v>
-      </c>
-      <c r="K101">
-        <v>5.800000000000001</v>
-      </c>
-      <c r="L101">
-        <v>37.53333333333333</v>
-      </c>
-      <c r="M101">
-        <v>16.2916182</v>
-      </c>
-      <c r="N101">
-        <v>21.24171513333333</v>
-      </c>
-      <c r="O101">
-        <v>4.673177329333332</v>
-      </c>
-      <c r="P101">
-        <v>16.568537804</v>
-      </c>
-      <c r="Q101">
-        <v>22.368537804</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.656760051889747</v>
-      </c>
-      <c r="T101">
-        <v>73.12961910570851</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.22</v>
-      </c>
-      <c r="W101">
-        <v>0.05912400000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.303843170921678</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
